--- a/src/assets/report-template.xlsx
+++ b/src/assets/report-template.xlsx
@@ -3080,7 +3080,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>디스플레이_상세!$B$74:$B$81</c:f>
+              <c:f>디스플레이_상세!$B$74:$B$82</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3112,7 +3112,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>디스플레이_상세!$K$74:$K$81</c:f>
+              <c:f>디스플레이_상세!$K$74:$K$82</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="8"/>
@@ -14547,7 +14547,7 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:N82"/>
+  <dimension ref="B2:N83"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -16149,55 +16149,104 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="2:14" ht="19.5" customHeight="1">
-      <c r="B82" s="8" t="s">
+    <row r="82" spans="2:14">
+      <c r="B82" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">알 수 없음</t>
+        </is>
+      </c>
+      <c r="C82" s="5">
+        <v>540000</v>
+      </c>
+      <c r="D82" s="5">
+        <v>2300</v>
+      </c>
+      <c r="E82" s="6">
+        <f t="shared" si="12"/>
+        <v>4.2592592592592595E-3</v>
+      </c>
+      <c r="F82" s="5">
+        <f t="shared" si="13"/>
+        <v>204.34782608695653</v>
+      </c>
+      <c r="G82" s="5">
+        <v>470000</v>
+      </c>
+      <c r="H82" s="5">
+        <f t="shared" si="14"/>
+        <v>35</v>
+      </c>
+      <c r="I82" s="6">
+        <f t="shared" si="15"/>
+        <v>1.5217391304347827E-2</v>
+      </c>
+      <c r="J82" s="5">
+        <f t="shared" si="16"/>
+        <v>13428.571428571429</v>
+      </c>
+      <c r="K82" s="5">
+        <v>850000</v>
+      </c>
+      <c r="L82" s="7">
+        <f t="shared" si="17"/>
+        <v>1.8085106382978724</v>
+      </c>
+      <c r="M82" s="5">
+        <v>18</v>
+      </c>
+      <c r="N82" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="2:14" ht="19.5" customHeight="1">
+      <c r="B83" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="12">
+      <c r="C83" s="12">
         <f>SUM(C74:C81)</f>
         <v>6050000</v>
       </c>
-      <c r="D82" s="12">
+      <c r="D83" s="12">
         <f>SUM(D74:D81)</f>
         <v>27800</v>
       </c>
-      <c r="E82" s="13">
+      <c r="E83" s="13">
         <f t="shared" si="12"/>
         <v>4.5950413223140498E-3</v>
       </c>
-      <c r="F82" s="12">
+      <c r="F83" s="12">
         <f t="shared" si="13"/>
         <v>193.88489208633092</v>
       </c>
-      <c r="G82" s="12">
+      <c r="G83" s="12">
         <f>SUM(G74:G81)</f>
         <v>5390000</v>
       </c>
-      <c r="H82" s="12">
+      <c r="H83" s="12">
         <f t="shared" si="14"/>
         <v>426</v>
       </c>
-      <c r="I82" s="13">
+      <c r="I83" s="13">
         <f t="shared" si="15"/>
         <v>1.5323741007194245E-2</v>
       </c>
-      <c r="J82" s="12">
+      <c r="J83" s="12">
         <f t="shared" si="16"/>
         <v>12652.582159624413</v>
       </c>
-      <c r="K82" s="12">
+      <c r="K83" s="12">
         <f>SUM(K74:K81)</f>
         <v>9400000</v>
       </c>
-      <c r="L82" s="14">
+      <c r="L83" s="14">
         <f t="shared" si="17"/>
         <v>1.7439703153988868</v>
       </c>
-      <c r="M82" s="12">
+      <c r="M83" s="12">
         <f>SUM(M74:M81)</f>
         <v>218</v>
       </c>
-      <c r="N82" s="12">
+      <c r="N83" s="12">
         <f>SUM(N74:N81)</f>
         <v>208</v>
       </c>

--- a/src/assets/report-template.xlsx
+++ b/src/assets/report-template.xlsx
@@ -6771,6 +6771,969 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16383</xdr:col>
+      <xdr:colOff>29308</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A69D5AE8-AA9F-589D-F398-7D2FBD757E36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7605346" cy="5092212"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>173935</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>223629</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4050195" cy="934936"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E20EDC74-29B8-6B5D-F46B-974740C23205}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="320473" y="963648"/>
+          <a:ext cx="4050195" cy="934936"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="3800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="E6783B"/>
+              </a:solidFill>
+              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>광고 리포트</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>168966</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>215347</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3914361" cy="969958"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BCF9ED0-4724-4264-A0F5-4CE6D187D022}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="315504" y="1512212"/>
+          <a:ext cx="3914361" cy="969958"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="4600" b="1">
+              <a:solidFill>
+                <a:srgbClr val="3A2A20"/>
+              </a:solidFill>
+              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>AD REPORT</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4600" b="1">
+            <a:solidFill>
+              <a:srgbClr val="3A2A20"/>
+            </a:solidFill>
+            <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>301490</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>124239</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1355032" cy="256761"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5B8C14A-B61F-45DD-A9A4-42F00042E737}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="442294" y="869674"/>
+          <a:ext cx="1355032" cy="256761"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E6783B"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>__ADV__</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>258731</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>276659</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>768569</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>276659</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="직선 연결선 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A0F44C1-FAAA-77F8-68B1-5D8DF472E23B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="403248" y="2588935"/>
+          <a:ext cx="509838" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="E6783B"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>142265</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>40000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1000000" cy="281672"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="lbl14"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="285140" y="3229514"/>
+          <a:ext cx="1000000" cy="281672"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>담당자</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>200000</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>40000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="150000" cy="281672"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="div14"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1181075" y="3229514"/>
+          <a:ext cx="150000" cy="281672"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>│</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>420000</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>40000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3200000" cy="281672"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="val14"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1401075" y="3229514"/>
+          <a:ext cx="3200000" cy="281672"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>__AUTHOR__</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>142265</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>40000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1000000" cy="281672"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="lbl15"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="285140" y="3515264"/>
+          <a:ext cx="1000000" cy="281672"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>리포트 기간</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>200000</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>40000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="150000" cy="281672"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="div15"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1181075" y="3515264"/>
+          <a:ext cx="150000" cy="281672"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>│</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>420000</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>40000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3200000" cy="281672"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="val15"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1401075" y="3515264"/>
+          <a:ext cx="3200000" cy="281672"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>__PERIOD__</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>142265</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>40000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1000000" cy="281672"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="lbl16"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="285140" y="3801014"/>
+          <a:ext cx="1000000" cy="281672"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>작성일</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>200000</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>40000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="150000" cy="281672"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="div16"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1181075" y="3801014"/>
+          <a:ext cx="150000" cy="281672"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>│</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>420000</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>40000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3200000" cy="281672"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="val16"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1401075" y="3801014"/>
+          <a:ext cx="3200000" cy="281672"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>__CREATED__</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>681403</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>177156</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2601058" cy="281672"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="TextBox 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{118A160B-9944-4E78-BC50-A89F9F630A6C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5004288" y="4771137"/>
+          <a:ext cx="2601058" cy="281672"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="F6D1BC"/>
+              </a:solidFill>
+              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>© </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="F6D1BC"/>
+              </a:solidFill>
+              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>디브이마케팅 주식회사</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="F6D1BC"/>
+              </a:solidFill>
+              <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            </a:rPr>
+            <a:t>. All rights reserved</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="800" b="0">
+            <a:solidFill>
+              <a:srgbClr val="F6D1BC"/>
+            </a:solidFill>
+            <a:latin typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6971,192 +7934,47 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B4:I18"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{709D7D18-03A1-4C0A-8111-ABE0436BAD28}">
+  <dimension ref="B1:P23"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.140625" customWidth="1"/>
     <col min="2" max="9" width="12.5703125" customWidth="1"/>
     <col min="10" max="10" width="2.140625" customWidth="1"/>
+    <col min="11" max="11" width="9" customWidth="1"/>
+    <col min="17" max="16383" width="8.7109375" hidden="1"/>
+    <col min="16384" max="16384" width="0.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:9" ht="13.5" customHeight="1">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="2:9" ht="18" customHeight="1">
-      <c r="B5" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-    </row>
-    <row r="6" spans="2:9" ht="3.75" customHeight="1">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="2:9" ht="21.75" customHeight="1">
-      <c r="B7" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-    </row>
-    <row r="8" spans="2:9" ht="21.75" customHeight="1">
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-    </row>
-    <row r="9" spans="2:9" ht="21" customHeight="1">
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-    </row>
-    <row r="10" spans="2:9" ht="15.75" customHeight="1"/>
-    <row r="11" spans="2:9" ht="21.75" customHeight="1">
-      <c r="B11" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-    </row>
-    <row r="12" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B12" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-    </row>
-    <row r="13" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B13" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-    </row>
-    <row r="14" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B14" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-    </row>
-    <row r="15" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B15" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-    </row>
-    <row r="16" spans="2:9" ht="22.5" customHeight="1">
-      <c r="B16" s="31" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-    </row>
-    <row r="18" spans="2:9" ht="21.75" customHeight="1">
-      <c r="B18" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-    </row>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4" ht="13.5" customHeight="1"/>
+    <row r="5" ht="18" customHeight="1"/>
+    <row r="6" ht="3.75" customHeight="1"/>
+    <row r="7" ht="21.75" customHeight="1"/>
+    <row r="8" ht="21.75" customHeight="1"/>
+    <row r="9" ht="21" customHeight="1"/>
+    <row r="10" ht="15.75" customHeight="1"/>
+    <row r="11" ht="21.75" customHeight="1"/>
+    <row r="12" ht="22.5" customHeight="1"/>
+    <row r="13" ht="22.5" customHeight="1"/>
+    <row r="14" ht="22.5" customHeight="1"/>
+    <row r="15" ht="22.5" customHeight="1"/>
+    <row r="16" ht="22.5" customHeight="1"/>
+    <row r="17"/>
+    <row r="18" ht="21.75" customHeight="1"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23" ht="9" customHeight="1"/>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B7:I9"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="B18:I18"/>
-  </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <sheetProtection sheet="1" scenarios="1"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/assets/report-template.xlsx
+++ b/src/assets/report-template.xlsx
@@ -19,6 +19,7 @@
     <sheet name="검색_상세" sheetId="4" r:id="rId4"/>
     <sheet name="파워링크_키워드" sheetId="5" r:id="rId5"/>
     <sheet name="쇼핑검색_키워드" sheetId="6" r:id="rId6"/>
+    <sheet name="쇼핑검색_상품" sheetId="9" r:id="rId13"/>
     <sheet name="디스플레이" sheetId="7" r:id="rId7"/>
     <sheet name="디스플레이_상세" sheetId="8" r:id="rId8"/>
   </sheets>
@@ -3267,6 +3268,632 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1400" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>일자별 광고비·매출</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>검색_상세!$G$14</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>검색_상세!$B$15:$B$21</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>검색_상세!$G$15:$G$21</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="60"/>
+        <c:overlap val="0"/>
+        <c:axId val="811110001"/>
+        <c:axId val="811110002"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>검색_상세!$K$14</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="21960">
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>검색_상세!$B$15:$B$21</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>검색_상세!$K$15:$K$21</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="811110003"/>
+        <c:axId val="811110004"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="811110001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="811110002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="811110002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="811110001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="811110004"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="811110003"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="811110003"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="811110004"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1400" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>일자별 광고비·매출</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>디스플레이_상세!$G$14</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>디스플레이_상세!$B$15:$B$21</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>디스플레이_상세!$G$15:$G$21</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="60"/>
+        <c:overlap val="0"/>
+        <c:axId val="811110001"/>
+        <c:axId val="811110002"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>디스플레이_상세!$K$14</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="21960">
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>디스플레이_상세!$B$15:$B$21</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>디스플레이_상세!$K$15:$K$21</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="811110003"/>
+        <c:axId val="811110004"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="811110001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="811110002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="811110002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="811110001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="811110004"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="811110003"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="811110003"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="811110004"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
 </c:chartSpace>
 </file>
 
@@ -7734,6 +8361,76 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>59070</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>714374</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>247650</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Chart 11"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>59070</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>714374</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>247650</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Chart 12"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -9524,7 +10221,7 @@
     <tabColor theme="8" tint="0.79998168889431442"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:O27"/>
+  <dimension ref="B2:O38"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -9553,1186 +10250,1197 @@
       <c r="M2" s="45"/>
       <c r="N2" s="45"/>
     </row>
-    <row r="3" spans="2:15" ht="30" customHeight="1">
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="2:15" ht="24" customHeight="1"/>
+    <row r="4" spans="2:15" ht="24" customHeight="1"/>
+    <row r="5" spans="2:15" ht="24" customHeight="1"/>
+    <row r="6" spans="2:15" ht="24" customHeight="1"/>
+    <row r="7" spans="2:15" ht="24" customHeight="1"/>
+    <row r="8" spans="2:15" ht="24" customHeight="1"/>
+    <row r="9" spans="2:15" ht="24" customHeight="1"/>
+    <row r="10" spans="2:15" ht="24" customHeight="1"/>
+    <row r="11" spans="2:15" ht="24" customHeight="1"/>
+    <row r="12" spans="2:15" ht="24" customHeight="1"/>
+    <row r="13" spans="2:15" ht="24" customHeight="1"/>
+    <row r="14" spans="2:15" ht="30" customHeight="1">
+      <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N14" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="18" customHeight="1">
-      <c r="B4" s="4" t="s">
+    <row r="15" spans="2:15" ht="18" customHeight="1">
+      <c r="B15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C15" s="5">
         <v>188200</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D15" s="5">
         <v>6510</v>
       </c>
-      <c r="E4" s="6">
-        <f>IFERROR(D4/C4,0)</f>
+      <c r="E15" s="6">
+        <f>IFERROR(D15/C15,0)</f>
         <v>3.4590860786397448E-2</v>
       </c>
-      <c r="F4" s="5">
-        <f>IFERROR(G4/D4,0)</f>
+      <c r="F15" s="5">
+        <f>IFERROR(G15/D15,0)</f>
         <v>948.38709677419354</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G15" s="5">
         <v>6174000</v>
       </c>
-      <c r="H4" s="5">
-        <f>M4+N4</f>
+      <c r="H15" s="5">
+        <f>M15+N15</f>
         <v>319</v>
       </c>
-      <c r="I4" s="6">
-        <f>IFERROR(H4/D4,0)</f>
+      <c r="I15" s="6">
+        <f>IFERROR(H15/D15,0)</f>
         <v>4.9001536098310289E-2</v>
       </c>
-      <c r="J4" s="5">
-        <f>IFERROR(G4/H4,0)</f>
+      <c r="J15" s="5">
+        <f>IFERROR(G15/H15,0)</f>
         <v>19354.231974921629</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K15" s="5">
         <v>16415000</v>
       </c>
-      <c r="L4" s="7">
-        <f>IFERROR(K4/G4,0)</f>
+      <c r="L15" s="7">
+        <f>IFERROR(K15/G15,0)</f>
         <v>2.6587301587301586</v>
       </c>
-      <c r="M4" s="23">
+      <c r="M15" s="23">
         <v>222</v>
       </c>
-      <c r="N4" s="23">
+      <c r="N15" s="23">
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="2:15" ht="18" customHeight="1">
-      <c r="B5" s="4" t="s">
+    <row r="16" spans="2:15" ht="18" customHeight="1">
+      <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C16" s="5">
         <v>179000</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D16" s="5">
         <v>6300</v>
       </c>
-      <c r="E5" s="6">
-        <f>IFERROR(D5/C5,0)</f>
+      <c r="E16" s="6">
+        <f>IFERROR(D16/C16,0)</f>
         <v>3.5195530726256981E-2</v>
       </c>
-      <c r="F5" s="5">
-        <f>IFERROR(G5/D5,0)</f>
+      <c r="F16" s="5">
+        <f>IFERROR(G16/D16,0)</f>
         <v>949.20634920634916</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G16" s="5">
         <v>5980000</v>
       </c>
-      <c r="H5" s="5">
-        <f>M5+N5</f>
+      <c r="H16" s="5">
+        <f>M16+N16</f>
         <v>302</v>
       </c>
-      <c r="I5" s="6">
-        <f>IFERROR(H5/D5,0)</f>
+      <c r="I16" s="6">
+        <f>IFERROR(H16/D16,0)</f>
         <v>4.7936507936507937E-2</v>
       </c>
-      <c r="J5" s="5">
-        <f>IFERROR(G5/H5,0)</f>
+      <c r="J16" s="5">
+        <f>IFERROR(G16/H16,0)</f>
         <v>19801.324503311258</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K16" s="5">
         <v>15600000</v>
       </c>
-      <c r="L5" s="7">
-        <f>IFERROR(K5/G5,0)</f>
+      <c r="L16" s="7">
+        <f>IFERROR(K16/G16,0)</f>
         <v>2.6086956521739131</v>
       </c>
-      <c r="M5" s="23">
+      <c r="M16" s="23">
         <v>210</v>
       </c>
-      <c r="N5" s="23">
+      <c r="N16" s="23">
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="18" customHeight="1">
-      <c r="B6" s="8" t="s">
+    <row r="17" spans="2:15" ht="18" customHeight="1">
+      <c r="B17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C17" s="9">
         <f t="shared" ref="C6:N6" si="0">C4-C5</f>
         <v>9200</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D17" s="9">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E17" s="10">
         <f t="shared" si="0"/>
         <v>-6.046699398595326E-4</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F17" s="9">
         <f t="shared" si="0"/>
         <v>-0.81925243215562205</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G17" s="9">
         <f t="shared" si="0"/>
         <v>194000</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H17" s="9">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
         <v>1.0650281618023519E-3</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J17" s="9">
         <f t="shared" si="0"/>
         <v>-447.09252838962857</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K17" s="9">
         <f t="shared" si="0"/>
         <v>815000</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L17" s="11">
         <f t="shared" si="0"/>
         <v>5.0034506556245528E-2</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M17" s="9">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="N6" s="9">
+      <c r="N17" s="9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:15" ht="18" customHeight="1">
-      <c r="B7" s="8" t="s">
+    <row r="18" spans="2:15" ht="18" customHeight="1">
+      <c r="B18" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C18" s="10">
         <f t="shared" ref="C7:N7" si="1">IFERROR((C4-C5)/C5,0)</f>
         <v>5.1396648044692739E-2</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D18" s="10">
         <f t="shared" si="1"/>
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E18" s="10">
         <f t="shared" si="1"/>
         <v>-1.7180304640453389E-2</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F18" s="10">
         <f t="shared" si="1"/>
         <v>-8.6309202718736107E-4</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G18" s="10">
         <f t="shared" si="1"/>
         <v>3.2441471571906355E-2</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H18" s="10">
         <f t="shared" si="1"/>
         <v>5.6291390728476824E-2</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I18" s="10">
         <f t="shared" si="1"/>
         <v>2.2217474898525883E-2</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
         <v>-2.2578920330044789E-2</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K18" s="10">
         <f t="shared" si="1"/>
         <v>5.2243589743589745E-2</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L18" s="10">
         <f t="shared" si="1"/>
         <v>1.917989417989412E-2</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M18" s="10">
         <f t="shared" si="1"/>
         <v>5.7142857142857141E-2</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N18" s="10">
         <f t="shared" si="1"/>
         <v>5.434782608695652E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:15" ht="24" customHeight="1">
-      <c r="B9" s="45" t="s">
+    <row r="20" spans="2:15" ht="24" customHeight="1">
+      <c r="B20" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="45"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="45"/>
-      <c r="O9" s="45"/>
-    </row>
-    <row r="10" spans="2:15" ht="30" customHeight="1">
-      <c r="B10" s="2" t="s">
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="45"/>
+    </row>
+    <row r="21" spans="2:15" ht="30" customHeight="1">
+      <c r="B21" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="L21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="O21" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="2:15">
-      <c r="B11" s="4" t="s">
+    <row r="22" spans="2:15">
+      <c r="B22" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D22" s="5">
         <v>25000</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E22" s="5">
         <v>720</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F22" s="6">
         <f t="shared" ref="F11:F27" si="2">IFERROR(E11/D11,0)</f>
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G22" s="5">
         <f t="shared" ref="G11:G27" si="3">IFERROR(H11/E11,0)</f>
         <v>1138.8888888888889</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H22" s="5">
         <v>820000</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I22" s="5">
         <f t="shared" ref="I11:I27" si="4">N11+O11</f>
         <v>42</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J22" s="6">
         <f t="shared" ref="J11:J27" si="5">IFERROR(I11/E11,0)</f>
         <v>5.8333333333333334E-2</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K22" s="5">
         <f t="shared" ref="K11:K27" si="6">IFERROR(H11/I11,0)</f>
         <v>19523.809523809523</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L22" s="5">
         <v>2900000</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M22" s="7">
         <f t="shared" ref="M11:M27" si="7">IFERROR(L11/H11,0)</f>
         <v>3.5365853658536586</v>
       </c>
-      <c r="N11" s="23">
+      <c r="N22" s="23">
         <v>30</v>
       </c>
-      <c r="O11" s="23">
+      <c r="O22" s="23">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="2:15">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4" t="s">
+    <row r="23" spans="2:15">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D23" s="5">
         <v>38000</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E23" s="5">
         <v>980</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F23" s="6">
         <f t="shared" si="2"/>
         <v>2.5789473684210525E-2</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G23" s="5">
         <f t="shared" si="3"/>
         <v>1142.8571428571429</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H23" s="5">
         <v>1120000</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I23" s="5">
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J23" s="6">
         <f t="shared" si="5"/>
         <v>2.6530612244897958E-2</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K23" s="5">
         <f t="shared" si="6"/>
         <v>43076.923076923078</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L23" s="5">
         <v>2400000</v>
       </c>
-      <c r="M12" s="7">
+      <c r="M23" s="7">
         <f t="shared" si="7"/>
         <v>2.1428571428571428</v>
       </c>
-      <c r="N12" s="23">
+      <c r="N23" s="23">
         <v>18</v>
       </c>
-      <c r="O12" s="23">
+      <c r="O23" s="23">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:15">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4" t="s">
+    <row r="24" spans="2:15">
+      <c r="B24" s="4"/>
+      <c r="C24" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D24" s="5">
         <v>20000</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E24" s="5">
         <v>540</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F24" s="6">
         <f t="shared" si="2"/>
         <v>2.7E-2</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G24" s="5">
         <f t="shared" si="3"/>
         <v>1037.037037037037</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H24" s="5">
         <v>560000</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I24" s="5">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J24" s="6">
         <f t="shared" si="5"/>
         <v>2.2222222222222223E-2</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K24" s="5">
         <f t="shared" si="6"/>
         <v>46666.666666666664</v>
       </c>
-      <c r="L13" s="5">
+      <c r="L24" s="5">
         <v>800000</v>
       </c>
-      <c r="M13" s="7">
+      <c r="M24" s="7">
         <f t="shared" si="7"/>
         <v>1.4285714285714286</v>
       </c>
-      <c r="N13" s="23">
+      <c r="N24" s="23">
         <v>8</v>
       </c>
-      <c r="O13" s="23">
+      <c r="O24" s="23">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="2:15">
-      <c r="B14" s="15" t="s">
+    <row r="25" spans="2:15">
+      <c r="B25" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C25" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="16">
-        <f>SUM(D11:D13)</f>
+      <c r="D25" s="16">
+        <f>SUM(D22:D24)</f>
         <v>83000</v>
       </c>
-      <c r="E14" s="16">
-        <f>SUM(E11:E13)</f>
+      <c r="E25" s="16">
+        <f>SUM(E22:E24)</f>
         <v>2240</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F25" s="17">
         <f t="shared" si="2"/>
         <v>2.6987951807228915E-2</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G25" s="16">
         <f t="shared" si="3"/>
         <v>1116.0714285714287</v>
       </c>
-      <c r="H14" s="16">
-        <f>SUM(H11:H13)</f>
+      <c r="H25" s="16">
+        <f>SUM(H22:H24)</f>
         <v>2500000</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I25" s="16">
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
-      <c r="J14" s="17">
+      <c r="J25" s="17">
         <f t="shared" si="5"/>
         <v>3.5714285714285712E-2</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K25" s="16">
         <f t="shared" si="6"/>
         <v>31250</v>
       </c>
-      <c r="L14" s="16">
-        <f>SUM(L11:L13)</f>
+      <c r="L25" s="16">
+        <f>SUM(L22:L24)</f>
         <v>6100000</v>
       </c>
-      <c r="M14" s="18">
+      <c r="M25" s="18">
         <f t="shared" si="7"/>
         <v>2.44</v>
       </c>
-      <c r="N14" s="24">
-        <f>SUM(N11:N13)</f>
+      <c r="N25" s="24">
+        <f>SUM(N22:N24)</f>
         <v>56</v>
       </c>
-      <c r="O14" s="24">
-        <f>SUM(O11:O13)</f>
+      <c r="O25" s="24">
+        <f>SUM(O22:O24)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="2:15">
-      <c r="B15" s="4" t="s">
+    <row r="26" spans="2:15">
+      <c r="B26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C26" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D26" s="5">
         <v>40000</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E26" s="5">
         <v>920</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F26" s="6">
         <f t="shared" si="2"/>
         <v>2.3E-2</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G26" s="5">
         <f t="shared" si="3"/>
         <v>1500</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H26" s="5">
         <v>1380000</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I26" s="5">
         <f t="shared" si="4"/>
         <v>132</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J26" s="6">
         <f t="shared" si="5"/>
         <v>0.14347826086956522</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K26" s="5">
         <f t="shared" si="6"/>
         <v>10454.545454545454</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L26" s="5">
         <v>3600000</v>
       </c>
-      <c r="M15" s="7">
+      <c r="M26" s="7">
         <f t="shared" si="7"/>
         <v>2.6086956521739131</v>
       </c>
-      <c r="N15" s="23">
+      <c r="N26" s="23">
         <v>90</v>
       </c>
-      <c r="O15" s="23">
+      <c r="O26" s="23">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="2:15">
-      <c r="B16" s="4"/>
-      <c r="C16" s="4" t="s">
+    <row r="27" spans="2:15">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D27" s="5">
         <v>18000</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E27" s="5">
         <v>320</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F27" s="6">
         <f t="shared" si="2"/>
         <v>1.7777777777777778E-2</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G27" s="5">
         <f t="shared" si="3"/>
         <v>1531.25</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H27" s="5">
         <v>490000</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I27" s="5">
         <f t="shared" si="4"/>
         <v>29</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J27" s="6">
         <f t="shared" si="5"/>
         <v>9.0624999999999997E-2</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K27" s="5">
         <f t="shared" si="6"/>
         <v>16896.551724137931</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L27" s="5">
         <v>1160000</v>
       </c>
-      <c r="M16" s="7">
+      <c r="M27" s="7">
         <f t="shared" si="7"/>
         <v>2.3673469387755102</v>
       </c>
-      <c r="N16" s="23">
+      <c r="N27" s="23">
         <v>20</v>
       </c>
-      <c r="O16" s="23">
+      <c r="O27" s="23">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="2:15">
-      <c r="B17" s="15" t="s">
+    <row r="28" spans="2:15">
+      <c r="B28" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C28" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="16">
-        <f>SUM(D15:D16)</f>
+      <c r="D28" s="16">
+        <f>SUM(D26:D27)</f>
         <v>58000</v>
       </c>
-      <c r="E17" s="16">
-        <f>SUM(E15:E16)</f>
+      <c r="E28" s="16">
+        <f>SUM(E26:E27)</f>
         <v>1240</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F28" s="17">
         <f t="shared" si="2"/>
         <v>2.1379310344827585E-2</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G28" s="16">
         <f t="shared" si="3"/>
         <v>1508.0645161290322</v>
       </c>
-      <c r="H17" s="16">
-        <f>SUM(H15:H16)</f>
+      <c r="H28" s="16">
+        <f>SUM(H26:H27)</f>
         <v>1870000</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I28" s="16">
         <f t="shared" si="4"/>
         <v>161</v>
       </c>
-      <c r="J17" s="17">
+      <c r="J28" s="17">
         <f t="shared" si="5"/>
         <v>0.12983870967741937</v>
       </c>
-      <c r="K17" s="16">
+      <c r="K28" s="16">
         <f t="shared" si="6"/>
         <v>11614.906832298137</v>
       </c>
-      <c r="L17" s="16">
-        <f>SUM(L15:L16)</f>
+      <c r="L28" s="16">
+        <f>SUM(L26:L27)</f>
         <v>4760000</v>
       </c>
-      <c r="M17" s="18">
+      <c r="M28" s="18">
         <f t="shared" si="7"/>
         <v>2.5454545454545454</v>
       </c>
-      <c r="N17" s="24">
-        <f>SUM(N15:N16)</f>
+      <c r="N28" s="24">
+        <f>SUM(N26:N27)</f>
         <v>110</v>
       </c>
-      <c r="O17" s="24">
-        <f>SUM(O15:O16)</f>
+      <c r="O28" s="24">
+        <f>SUM(O26:O27)</f>
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="2:15">
-      <c r="B18" s="4" t="s">
+    <row r="29" spans="2:15">
+      <c r="B29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C29" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D29" s="5">
         <v>12000</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E29" s="5">
         <v>340</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F29" s="6">
         <f t="shared" si="2"/>
         <v>2.8333333333333332E-2</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G29" s="5">
         <f t="shared" si="3"/>
         <v>300</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H29" s="5">
         <v>102000</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I29" s="5">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J29" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K29" s="5">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L29" s="5">
         <v>0</v>
       </c>
-      <c r="M18" s="7">
+      <c r="M29" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N18" s="23">
+      <c r="N29" s="23">
         <v>0</v>
       </c>
-      <c r="O18" s="23">
+      <c r="O29" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:15">
-      <c r="B19" s="4"/>
-      <c r="C19" s="4" t="s">
+    <row r="30" spans="2:15">
+      <c r="B30" s="4"/>
+      <c r="C30" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D30" s="5">
         <v>8500</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E30" s="5">
         <v>180</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F30" s="6">
         <f t="shared" si="2"/>
         <v>2.1176470588235293E-2</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G30" s="5">
         <f t="shared" si="3"/>
         <v>300</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H30" s="5">
         <v>54000</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I30" s="5">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J30" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K30" s="5">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L30" s="5">
         <v>0</v>
       </c>
-      <c r="M19" s="7">
+      <c r="M30" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N19" s="23">
+      <c r="N30" s="23">
         <v>0</v>
       </c>
-      <c r="O19" s="23">
+      <c r="O30" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:15">
-      <c r="B20" s="15" t="s">
+    <row r="31" spans="2:15">
+      <c r="B31" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C31" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="16">
-        <f>SUM(D18:D19)</f>
+      <c r="D31" s="16">
+        <f>SUM(D29:D30)</f>
         <v>20500</v>
       </c>
-      <c r="E20" s="16">
-        <f>SUM(E18:E19)</f>
+      <c r="E31" s="16">
+        <f>SUM(E29:E30)</f>
         <v>520</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F31" s="17">
         <f t="shared" si="2"/>
         <v>2.5365853658536587E-2</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G31" s="16">
         <f t="shared" si="3"/>
         <v>300</v>
       </c>
-      <c r="H20" s="16">
-        <f>SUM(H18:H19)</f>
+      <c r="H31" s="16">
+        <f>SUM(H29:H30)</f>
         <v>156000</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I31" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J20" s="17">
+      <c r="J31" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K31" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L20" s="16">
-        <f>SUM(L18:L19)</f>
+      <c r="L31" s="16">
+        <f>SUM(L29:L30)</f>
         <v>0</v>
       </c>
-      <c r="M20" s="18">
+      <c r="M31" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N20" s="24">
-        <f>SUM(N18:N19)</f>
+      <c r="N31" s="24">
+        <f>SUM(N29:N30)</f>
         <v>0</v>
       </c>
-      <c r="O20" s="24">
-        <f>SUM(O18:O19)</f>
+      <c r="O31" s="24">
+        <f>SUM(O29:O30)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:15">
-      <c r="B21" s="4" t="s">
+    <row r="32" spans="2:15">
+      <c r="B32" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D32" s="5">
         <v>18500</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E32" s="5">
         <v>2400</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F32" s="6">
         <f t="shared" si="2"/>
         <v>0.12972972972972974</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G32" s="5">
         <f t="shared" si="3"/>
         <v>625</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H32" s="5">
         <v>1500000</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I32" s="5">
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J32" s="6">
         <f t="shared" si="5"/>
         <v>3.125E-2</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K32" s="5">
         <f t="shared" si="6"/>
         <v>20000</v>
       </c>
-      <c r="L21" s="5">
+      <c r="L32" s="5">
         <v>4200000</v>
       </c>
-      <c r="M21" s="7">
+      <c r="M32" s="7">
         <f t="shared" si="7"/>
         <v>2.8</v>
       </c>
-      <c r="N21" s="23">
+      <c r="N32" s="23">
         <v>55</v>
       </c>
-      <c r="O21" s="23">
+      <c r="O32" s="23">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="2:15">
-      <c r="B22" s="4"/>
-      <c r="C22" s="4" t="s">
+    <row r="33" spans="2:15">
+      <c r="B33" s="4"/>
+      <c r="C33" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D33" s="5">
         <v>9200</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E33" s="5">
         <v>880</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F33" s="6">
         <f t="shared" si="2"/>
         <v>9.5652173913043481E-2</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G33" s="5">
         <f t="shared" si="3"/>
         <v>1136.3636363636363</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H33" s="5">
         <v>1000000</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I33" s="5">
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J33" s="6">
         <f t="shared" si="5"/>
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="K22" s="5">
+      <c r="K33" s="5">
         <f t="shared" si="6"/>
         <v>45454.545454545456</v>
       </c>
-      <c r="L22" s="5">
+      <c r="L33" s="5">
         <v>1100000</v>
       </c>
-      <c r="M22" s="7">
+      <c r="M33" s="7">
         <f t="shared" si="7"/>
         <v>1.1000000000000001</v>
       </c>
-      <c r="N22" s="23">
+      <c r="N33" s="23">
         <v>15</v>
       </c>
-      <c r="O22" s="23">
+      <c r="O33" s="23">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="2:15">
-      <c r="B23" s="15" t="s">
+    <row r="34" spans="2:15">
+      <c r="B34" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C34" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="16">
-        <f>SUM(D21:D22)</f>
+      <c r="D34" s="16">
+        <f>SUM(D32:D33)</f>
         <v>27700</v>
       </c>
-      <c r="E23" s="16">
-        <f>SUM(E21:E22)</f>
+      <c r="E34" s="16">
+        <f>SUM(E32:E33)</f>
         <v>3280</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F34" s="17">
         <f t="shared" si="2"/>
         <v>0.1184115523465704</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G34" s="16">
         <f t="shared" si="3"/>
         <v>762.19512195121956</v>
       </c>
-      <c r="H23" s="16">
-        <f>SUM(H21:H22)</f>
+      <c r="H34" s="16">
+        <f>SUM(H32:H33)</f>
         <v>2500000</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I34" s="16">
         <f t="shared" si="4"/>
         <v>97</v>
       </c>
-      <c r="J23" s="17">
+      <c r="J34" s="17">
         <f t="shared" si="5"/>
         <v>2.9573170731707316E-2</v>
       </c>
-      <c r="K23" s="16">
+      <c r="K34" s="16">
         <f t="shared" si="6"/>
         <v>25773.195876288661</v>
       </c>
-      <c r="L23" s="16">
-        <f>SUM(L21:L22)</f>
+      <c r="L34" s="16">
+        <f>SUM(L32:L33)</f>
         <v>5300000</v>
       </c>
-      <c r="M23" s="18">
+      <c r="M34" s="18">
         <f t="shared" si="7"/>
         <v>2.12</v>
       </c>
-      <c r="N23" s="24">
-        <f>SUM(N21:N22)</f>
+      <c r="N34" s="24">
+        <f>SUM(N32:N33)</f>
         <v>70</v>
       </c>
-      <c r="O23" s="24">
-        <f>SUM(O21:O22)</f>
+      <c r="O34" s="24">
+        <f>SUM(O32:O33)</f>
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:15">
-      <c r="B24" s="4" t="s">
+    <row r="35" spans="2:15">
+      <c r="B35" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C35" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D35" s="5">
         <v>22000</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E35" s="5">
         <v>310</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F35" s="6">
         <f t="shared" si="2"/>
         <v>1.4090909090909091E-2</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G35" s="5">
         <f t="shared" si="3"/>
         <v>1200</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H35" s="5">
         <v>372000</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I35" s="5">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="J24" s="6">
+      <c r="J35" s="6">
         <f t="shared" si="5"/>
         <v>3.5483870967741936E-2</v>
       </c>
-      <c r="K24" s="5">
+      <c r="K35" s="5">
         <f t="shared" si="6"/>
         <v>33818.181818181816</v>
       </c>
-      <c r="L24" s="5">
+      <c r="L35" s="5">
         <v>360000</v>
       </c>
-      <c r="M24" s="7">
+      <c r="M35" s="7">
         <f t="shared" si="7"/>
         <v>0.967741935483871</v>
       </c>
-      <c r="N24" s="23">
+      <c r="N35" s="23">
         <v>7</v>
       </c>
-      <c r="O24" s="23">
+      <c r="O35" s="23">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="2:15">
-      <c r="B25" s="4"/>
-      <c r="C25" s="4" t="s">
+    <row r="36" spans="2:15">
+      <c r="B36" s="4"/>
+      <c r="C36" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D36" s="5">
         <v>15000</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E36" s="5">
         <v>180</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F36" s="6">
         <f t="shared" si="2"/>
         <v>1.2E-2</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G36" s="5">
         <f t="shared" si="3"/>
         <v>1100</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H36" s="5">
         <v>198000</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I36" s="5">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J36" s="6">
         <f t="shared" si="5"/>
         <v>4.4444444444444446E-2</v>
       </c>
-      <c r="K25" s="5">
+      <c r="K36" s="5">
         <f t="shared" si="6"/>
         <v>24750</v>
       </c>
-      <c r="L25" s="5">
+      <c r="L36" s="5">
         <v>175000</v>
       </c>
-      <c r="M25" s="7">
+      <c r="M36" s="7">
         <f t="shared" si="7"/>
         <v>0.88383838383838387</v>
       </c>
-      <c r="N25" s="23">
+      <c r="N36" s="23">
         <v>5</v>
       </c>
-      <c r="O25" s="23">
+      <c r="O36" s="23">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="2:15">
-      <c r="B26" s="15" t="s">
+    <row r="37" spans="2:15">
+      <c r="B37" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C37" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="16">
-        <f>SUM(D24:D25)</f>
+      <c r="D37" s="16">
+        <f>SUM(D35:D36)</f>
         <v>37000</v>
       </c>
-      <c r="E26" s="16">
-        <f>SUM(E24:E25)</f>
+      <c r="E37" s="16">
+        <f>SUM(E35:E36)</f>
         <v>490</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F37" s="17">
         <f t="shared" si="2"/>
         <v>1.3243243243243243E-2</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G37" s="16">
         <f t="shared" si="3"/>
         <v>1163.2653061224489</v>
       </c>
-      <c r="H26" s="16">
-        <f>SUM(H24:H25)</f>
+      <c r="H37" s="16">
+        <f>SUM(H35:H36)</f>
         <v>570000</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I37" s="16">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="J26" s="17">
+      <c r="J37" s="17">
         <f t="shared" si="5"/>
         <v>3.8775510204081633E-2</v>
       </c>
-      <c r="K26" s="16">
+      <c r="K37" s="16">
         <f t="shared" si="6"/>
         <v>30000</v>
       </c>
-      <c r="L26" s="16">
-        <f>SUM(L24:L25)</f>
+      <c r="L37" s="16">
+        <f>SUM(L35:L36)</f>
         <v>535000</v>
       </c>
-      <c r="M26" s="18">
+      <c r="M37" s="18">
         <f t="shared" si="7"/>
         <v>0.93859649122807021</v>
       </c>
-      <c r="N26" s="24">
-        <f>SUM(N24:N25)</f>
+      <c r="N37" s="24">
+        <f>SUM(N35:N36)</f>
         <v>12</v>
       </c>
-      <c r="O26" s="24">
-        <f>SUM(O24:O25)</f>
+      <c r="O37" s="24">
+        <f>SUM(O35:O36)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="2:15">
-      <c r="B27" s="30" t="s">
+    <row r="38" spans="2:15">
+      <c r="B38" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="30"/>
-      <c r="D27" s="12">
-        <f>D14+D17+D20+D23+D26</f>
+      <c r="C38" s="30"/>
+      <c r="D38" s="12">
+        <f>D25+D28+D31+D34+D37</f>
         <v>226200</v>
       </c>
-      <c r="E27" s="12">
-        <f>E14+E17+E20+E23+E26</f>
+      <c r="E38" s="12">
+        <f>E25+E28+E31+E34+E37</f>
         <v>7770</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F38" s="13">
         <f t="shared" si="2"/>
         <v>3.4350132625994692E-2</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G38" s="12">
         <f t="shared" si="3"/>
         <v>977.60617760617765</v>
       </c>
-      <c r="H27" s="12">
-        <f>H14+H17+H20+H23+H26</f>
+      <c r="H38" s="12">
+        <f>H25+H28+H31+H34+H37</f>
         <v>7596000</v>
       </c>
-      <c r="I27" s="12">
+      <c r="I38" s="12">
         <f t="shared" si="4"/>
         <v>357</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J38" s="13">
         <f t="shared" si="5"/>
         <v>4.5945945945945948E-2</v>
       </c>
-      <c r="K27" s="12">
+      <c r="K38" s="12">
         <f t="shared" si="6"/>
         <v>21277.310924369747</v>
       </c>
-      <c r="L27" s="12">
-        <f>L14+L17+L20+L23+L26</f>
+      <c r="L38" s="12">
+        <f>L25+L28+L31+L34+L37</f>
         <v>16695000</v>
       </c>
-      <c r="M27" s="14">
+      <c r="M38" s="14">
         <f t="shared" si="7"/>
         <v>2.1978672985781991</v>
       </c>
-      <c r="N27" s="25">
-        <f>N14+N17+N20+N23+N26</f>
+      <c r="N38" s="25">
+        <f>N25+N28+N31+N34+N37</f>
         <v>248</v>
       </c>
-      <c r="O27" s="25">
-        <f>O14+O17+O20+O23+O26</f>
+      <c r="O38" s="25">
+        <f>O25+O28+O31+O34+O37</f>
         <v>109</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B9:O9"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B20:O20"/>
+    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="C6:N7">
@@ -10745,6 +11453,7 @@
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13723,7 +14432,7 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:O35"/>
+  <dimension ref="B2:O46"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -13750,1410 +14459,853 @@
       <c r="M2" s="49"/>
       <c r="N2" s="49"/>
     </row>
-    <row r="3" spans="2:15" ht="30" customHeight="1">
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="2:15" ht="24" customHeight="1"/>
+    <row r="4" spans="2:15" ht="24" customHeight="1"/>
+    <row r="5" spans="2:15" ht="24" customHeight="1"/>
+    <row r="6" spans="2:15" ht="24" customHeight="1"/>
+    <row r="7" spans="2:15" ht="24" customHeight="1"/>
+    <row r="8" spans="2:15" ht="24" customHeight="1"/>
+    <row r="9" spans="2:15" ht="24" customHeight="1"/>
+    <row r="10" spans="2:15" ht="24" customHeight="1"/>
+    <row r="11" spans="2:15" ht="24" customHeight="1"/>
+    <row r="12" spans="2:15" ht="24" customHeight="1"/>
+    <row r="13" spans="2:15" ht="24" customHeight="1"/>
+    <row r="14" spans="2:15" ht="30" customHeight="1">
+      <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N14" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="18" customHeight="1">
-      <c r="B4" s="4" t="s">
+    <row r="15" spans="2:15" ht="18" customHeight="1">
+      <c r="B15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C15" s="5">
         <v>7051000</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D15" s="5">
         <v>35884</v>
       </c>
-      <c r="E4" s="6">
-        <f>IFERROR(D4/C4,0)</f>
+      <c r="E15" s="6">
+        <f>IFERROR(D15/C15,0)</f>
         <v>5.0892072046518225E-3</v>
       </c>
-      <c r="F4" s="5">
-        <f>IFERROR(G4/D4,0)</f>
+      <c r="F15" s="5">
+        <f>IFERROR(G15/D15,0)</f>
         <v>219.84728569836139</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G15" s="5">
         <v>7889000</v>
       </c>
-      <c r="H4" s="5">
-        <f>M4+N4</f>
+      <c r="H15" s="5">
+        <f>M15+N15</f>
         <v>1038</v>
       </c>
-      <c r="I4" s="6">
-        <f>IFERROR(H4/D4,0)</f>
+      <c r="I15" s="6">
+        <f>IFERROR(H15/D15,0)</f>
         <v>2.8926541076803033E-2</v>
       </c>
-      <c r="J4" s="5">
-        <f>IFERROR(G4/H4,0)</f>
+      <c r="J15" s="5">
+        <f>IFERROR(G15/H15,0)</f>
         <v>7600.1926782273604</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K15" s="5">
         <v>11478000</v>
       </c>
-      <c r="L4" s="7">
-        <f>IFERROR(K4/G4,0)</f>
+      <c r="L15" s="7">
+        <f>IFERROR(K15/G15,0)</f>
         <v>1.4549372544048675</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M15" s="5">
         <v>651</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N15" s="5">
         <v>387</v>
       </c>
     </row>
-    <row r="5" spans="2:15" ht="18" customHeight="1">
-      <c r="B5" s="4" t="s">
+    <row r="16" spans="2:15" ht="18" customHeight="1">
+      <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C16" s="5">
         <v>6800000</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D16" s="5">
         <v>34500</v>
       </c>
-      <c r="E5" s="6">
-        <f>IFERROR(D5/C5,0)</f>
+      <c r="E16" s="6">
+        <f>IFERROR(D16/C16,0)</f>
         <v>5.0735294117647059E-3</v>
       </c>
-      <c r="F5" s="5">
-        <f>IFERROR(G5/D5,0)</f>
+      <c r="F16" s="5">
+        <f>IFERROR(G16/D16,0)</f>
         <v>220.28985507246378</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G16" s="5">
         <v>7600000</v>
       </c>
-      <c r="H5" s="5">
-        <f>M5+N5</f>
+      <c r="H16" s="5">
+        <f>M16+N16</f>
         <v>980</v>
       </c>
-      <c r="I5" s="6">
-        <f>IFERROR(H5/D5,0)</f>
+      <c r="I16" s="6">
+        <f>IFERROR(H16/D16,0)</f>
         <v>2.8405797101449276E-2</v>
       </c>
-      <c r="J5" s="5">
-        <f>IFERROR(G5/H5,0)</f>
+      <c r="J16" s="5">
+        <f>IFERROR(G16/H16,0)</f>
         <v>7755.1020408163267</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K16" s="5">
         <v>10900000</v>
       </c>
-      <c r="L5" s="7">
-        <f>IFERROR(K5/G5,0)</f>
+      <c r="L16" s="7">
+        <f>IFERROR(K16/G16,0)</f>
         <v>1.4342105263157894</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M16" s="5">
         <v>620</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N16" s="5">
         <v>360</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="18" customHeight="1">
-      <c r="B6" s="8" t="s">
+    <row r="17" spans="2:15" ht="18" customHeight="1">
+      <c r="B17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C17" s="9">
         <f t="shared" ref="C6:N6" si="0">C4-C5</f>
         <v>251000</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D17" s="9">
         <f t="shared" si="0"/>
         <v>1384</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E17" s="10">
         <f t="shared" si="0"/>
         <v>1.5677792887116605E-5</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F17" s="9">
         <f t="shared" si="0"/>
         <v>-0.44256937410239061</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G17" s="9">
         <f t="shared" si="0"/>
         <v>289000</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H17" s="9">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
         <v>5.2074397535375669E-4</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J17" s="9">
         <f t="shared" si="0"/>
         <v>-154.90936258896636</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K17" s="9">
         <f t="shared" si="0"/>
         <v>578000</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L17" s="11">
         <f t="shared" si="0"/>
         <v>2.0726728089078161E-2</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M17" s="9">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="N6" s="9">
+      <c r="N17" s="9">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:15" ht="18" customHeight="1">
-      <c r="B7" s="8" t="s">
+    <row r="18" spans="2:15" ht="18" customHeight="1">
+      <c r="B18" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C18" s="10">
         <f t="shared" ref="C7:N7" si="1">IFERROR((C4-C5)/C5,0)</f>
         <v>3.6911764705882352E-2</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D18" s="10">
         <f t="shared" si="1"/>
         <v>4.011594202898551E-2</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E18" s="10">
         <f t="shared" si="1"/>
         <v>3.0901156994896498E-3</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F18" s="10">
         <f t="shared" si="1"/>
         <v>-2.0090320271753258E-3</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G18" s="10">
         <f t="shared" si="1"/>
         <v>3.8026315789473686E-2</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H18" s="10">
         <f t="shared" si="1"/>
         <v>5.9183673469387757E-2</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I18" s="10">
         <f t="shared" si="1"/>
         <v>1.8332313418065925E-2</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
         <v>-1.9975154649629873E-2</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K18" s="10">
         <f t="shared" si="1"/>
         <v>5.3027522935779815E-2</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L18" s="10">
         <f t="shared" si="1"/>
         <v>1.4451663621742572E-2</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M18" s="10">
         <f t="shared" si="1"/>
         <v>0.05</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N18" s="10">
         <f t="shared" si="1"/>
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:15" ht="24" customHeight="1">
-      <c r="B9" s="49" t="s">
+    <row r="20" spans="2:15" ht="24" customHeight="1">
+      <c r="B20" s="49" t="s">
         <v>149</v>
       </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="49"/>
-      <c r="N9" s="49"/>
-      <c r="O9" s="49"/>
-    </row>
-    <row r="10" spans="2:15" ht="30" customHeight="1">
-      <c r="B10" s="2" t="s">
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="49"/>
+      <c r="L20" s="49"/>
+      <c r="M20" s="49"/>
+      <c r="N20" s="49"/>
+      <c r="O20" s="49"/>
+    </row>
+    <row r="21" spans="2:15" ht="30" customHeight="1">
+      <c r="B21" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="51" t="s">
+      <c r="J21" s="51" t="s">
         <v>145</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="L21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="O21" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="2:15">
-      <c r="B11" s="4" t="s">
+    <row r="22" spans="2:15">
+      <c r="B22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D22" s="5">
         <v>643000</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E22" s="5">
         <v>5795</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F22" s="6">
         <f t="shared" ref="F11:F35" si="2">IFERROR(E11/D11,0)</f>
         <v>9.0124416796267502E-3</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G22" s="5">
         <f t="shared" ref="G11:G35" si="3">IFERROR(H11/E11,0)</f>
         <v>223.64106988783433</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H22" s="5">
         <v>1296000</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I22" s="5">
         <f t="shared" ref="I11:I35" si="4">N11+O11</f>
         <v>76</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J22" s="6">
         <f t="shared" ref="J11:J35" si="5">IFERROR(I11/E11,0)</f>
         <v>1.3114754098360656E-2</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K22" s="5">
         <f t="shared" ref="K11:K35" si="6">IFERROR(H11/I11,0)</f>
         <v>17052.63157894737</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L22" s="5">
         <v>926000</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M22" s="7">
         <f t="shared" ref="M11:M35" si="7">IFERROR(L11/H11,0)</f>
         <v>0.71450617283950613</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N22" s="5">
         <v>50</v>
       </c>
-      <c r="O11" s="5">
+      <c r="O22" s="5">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:15">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4" t="s">
+    <row r="23" spans="2:15">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D23" s="5">
         <v>410000</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E23" s="5">
         <v>3200</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F23" s="6">
         <f t="shared" si="2"/>
         <v>7.8048780487804878E-3</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G23" s="5">
         <f t="shared" si="3"/>
         <v>225</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H23" s="5">
         <v>720000</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I23" s="5">
         <f t="shared" si="4"/>
         <v>46</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J23" s="6">
         <f t="shared" si="5"/>
         <v>1.4375000000000001E-2</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K23" s="5">
         <f t="shared" si="6"/>
         <v>15652.173913043478</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L23" s="5">
         <v>540000</v>
       </c>
-      <c r="M12" s="7">
+      <c r="M23" s="7">
         <f t="shared" si="7"/>
         <v>0.75</v>
       </c>
-      <c r="N12" s="5">
+      <c r="N23" s="5">
         <v>30</v>
       </c>
-      <c r="O12" s="5">
+      <c r="O23" s="5">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="2:15">
-      <c r="B13" s="15" t="s">
+    <row r="24" spans="2:15">
+      <c r="B24" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C24" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="16">
-        <f>SUM(D11:D12)</f>
+      <c r="D24" s="16">
+        <f>SUM(D22:D23)</f>
         <v>1053000</v>
       </c>
-      <c r="E13" s="16">
-        <f>SUM(E11:E12)</f>
+      <c r="E24" s="16">
+        <f>SUM(E22:E23)</f>
         <v>8995</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F24" s="17">
         <f t="shared" si="2"/>
         <v>8.5422602089268752E-3</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G24" s="16">
         <f t="shared" si="3"/>
         <v>224.12451361867704</v>
       </c>
-      <c r="H13" s="16">
-        <f>SUM(H11:H12)</f>
+      <c r="H24" s="16">
+        <f>SUM(H22:H23)</f>
         <v>2016000</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I24" s="16">
         <f t="shared" si="4"/>
         <v>122</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J24" s="17">
         <f t="shared" si="5"/>
         <v>1.3563090605892163E-2</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K24" s="16">
         <f t="shared" si="6"/>
         <v>16524.590163934427</v>
       </c>
-      <c r="L13" s="16">
-        <f>SUM(L11:L12)</f>
+      <c r="L24" s="16">
+        <f>SUM(L22:L23)</f>
         <v>1466000</v>
       </c>
-      <c r="M13" s="18">
+      <c r="M24" s="18">
         <f t="shared" si="7"/>
         <v>0.72718253968253965</v>
       </c>
-      <c r="N13" s="16">
-        <f>SUM(N11:N12)</f>
+      <c r="N24" s="16">
+        <f>SUM(N22:N23)</f>
         <v>80</v>
       </c>
-      <c r="O13" s="16">
-        <f>SUM(O11:O12)</f>
+      <c r="O24" s="16">
+        <f>SUM(O22:O23)</f>
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:15">
-      <c r="B14" s="4" t="s">
+    <row r="25" spans="2:15">
+      <c r="B25" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C25" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D25" s="5">
         <v>520000</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E25" s="5">
         <v>4100</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F25" s="6">
         <f t="shared" si="2"/>
         <v>7.884615384615384E-3</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G25" s="5">
         <f t="shared" si="3"/>
         <v>214.63414634146341</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H25" s="5">
         <v>880000</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I25" s="5">
         <f t="shared" si="4"/>
         <v>320</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J25" s="6">
         <f t="shared" si="5"/>
         <v>7.8048780487804878E-2</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K25" s="5">
         <f t="shared" si="6"/>
         <v>2750</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L25" s="5">
         <v>1700000</v>
       </c>
-      <c r="M14" s="7">
+      <c r="M25" s="7">
         <f t="shared" si="7"/>
         <v>1.9318181818181819</v>
       </c>
-      <c r="N14" s="5">
+      <c r="N25" s="5">
         <v>200</v>
       </c>
-      <c r="O14" s="5">
+      <c r="O25" s="5">
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="2:15">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4" t="s">
+    <row r="26" spans="2:15">
+      <c r="B26" s="4"/>
+      <c r="C26" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D26" s="5">
         <v>310000</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E26" s="5">
         <v>2050</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F26" s="6">
         <f t="shared" si="2"/>
         <v>6.6129032258064515E-3</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G26" s="5">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H26" s="5">
         <v>410000</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I26" s="5">
         <f t="shared" si="4"/>
         <v>170</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J26" s="6">
         <f t="shared" si="5"/>
         <v>8.2926829268292687E-2</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K26" s="5">
         <f t="shared" si="6"/>
         <v>2411.7647058823532</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L26" s="5">
         <v>760000</v>
       </c>
-      <c r="M15" s="7">
+      <c r="M26" s="7">
         <f t="shared" si="7"/>
         <v>1.8536585365853659</v>
       </c>
-      <c r="N15" s="5">
+      <c r="N26" s="5">
         <v>100</v>
       </c>
-      <c r="O15" s="5">
+      <c r="O26" s="5">
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="2:15">
-      <c r="B16" s="15" t="s">
+    <row r="27" spans="2:15">
+      <c r="B27" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C27" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="16">
-        <f>SUM(D14:D15)</f>
+      <c r="D27" s="16">
+        <f>SUM(D25:D26)</f>
         <v>830000</v>
       </c>
-      <c r="E16" s="16">
-        <f>SUM(E14:E15)</f>
+      <c r="E27" s="16">
+        <f>SUM(E25:E26)</f>
         <v>6150</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F27" s="17">
         <f t="shared" si="2"/>
         <v>7.4096385542168674E-3</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G27" s="16">
         <f t="shared" si="3"/>
         <v>209.7560975609756</v>
       </c>
-      <c r="H16" s="16">
-        <f>SUM(H14:H15)</f>
+      <c r="H27" s="16">
+        <f>SUM(H25:H26)</f>
         <v>1290000</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I27" s="16">
         <f t="shared" si="4"/>
         <v>490</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J27" s="17">
         <f t="shared" si="5"/>
         <v>7.9674796747967486E-2</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K27" s="16">
         <f t="shared" si="6"/>
         <v>2632.6530612244896</v>
       </c>
-      <c r="L16" s="16">
-        <f>SUM(L14:L15)</f>
+      <c r="L27" s="16">
+        <f>SUM(L25:L26)</f>
         <v>2460000</v>
       </c>
-      <c r="M16" s="18">
+      <c r="M27" s="18">
         <f t="shared" si="7"/>
         <v>1.9069767441860466</v>
       </c>
-      <c r="N16" s="16">
-        <f>SUM(N14:N15)</f>
+      <c r="N27" s="16">
+        <f>SUM(N25:N26)</f>
         <v>300</v>
       </c>
-      <c r="O16" s="16">
-        <f>SUM(O14:O15)</f>
+      <c r="O27" s="16">
+        <f>SUM(O25:O26)</f>
         <v>190</v>
       </c>
     </row>
-    <row r="17" spans="2:15">
-      <c r="B17" s="4" t="s">
+    <row r="28" spans="2:15">
+      <c r="B28" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C28" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D28" s="5">
         <v>1297000</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E28" s="5">
         <v>5795</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F28" s="6">
         <f t="shared" si="2"/>
         <v>4.4680030840400925E-3</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G28" s="5">
         <f t="shared" si="3"/>
         <v>223.64106988783433</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H28" s="5">
         <v>1296000</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I28" s="5">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J28" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K17" s="5">
+      <c r="K28" s="5">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L17" s="5">
+      <c r="L28" s="5">
         <v>0</v>
       </c>
-      <c r="M17" s="7">
+      <c r="M28" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N17" s="5">
+      <c r="N28" s="5">
         <v>0</v>
       </c>
-      <c r="O17" s="5">
+      <c r="O28" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:15">
-      <c r="B18" s="4"/>
-      <c r="C18" s="4" t="s">
+    <row r="29" spans="2:15">
+      <c r="B29" s="4"/>
+      <c r="C29" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D29" s="5">
         <v>820000</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E29" s="5">
         <v>3100</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F29" s="6">
         <f t="shared" si="2"/>
         <v>3.7804878048780487E-3</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G29" s="5">
         <f t="shared" si="3"/>
         <v>225.80645161290323</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H29" s="5">
         <v>700000</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I29" s="5">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J29" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K29" s="5">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L29" s="5">
         <v>0</v>
       </c>
-      <c r="M18" s="7">
+      <c r="M29" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N18" s="5">
+      <c r="N29" s="5">
         <v>0</v>
       </c>
-      <c r="O18" s="5">
+      <c r="O29" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:15">
-      <c r="B19" s="15" t="s">
+    <row r="30" spans="2:15">
+      <c r="B30" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C30" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="16">
-        <f>SUM(D17:D18)</f>
+      <c r="D30" s="16">
+        <f>SUM(D28:D29)</f>
         <v>2117000</v>
       </c>
-      <c r="E19" s="16">
-        <f>SUM(E17:E18)</f>
+      <c r="E30" s="16">
+        <f>SUM(E28:E29)</f>
         <v>8895</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F30" s="17">
         <f t="shared" si="2"/>
         <v>4.2017005196032121E-3</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G30" s="16">
         <f t="shared" si="3"/>
         <v>224.39572793704329</v>
       </c>
-      <c r="H19" s="16">
-        <f>SUM(H17:H18)</f>
+      <c r="H30" s="16">
+        <f>SUM(H28:H29)</f>
         <v>1996000</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I30" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J19" s="17">
+      <c r="J30" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K19" s="16">
+      <c r="K30" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L19" s="16">
-        <f>SUM(L17:L18)</f>
+      <c r="L30" s="16">
+        <f>SUM(L28:L29)</f>
         <v>0</v>
       </c>
-      <c r="M19" s="18">
+      <c r="M30" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N19" s="16">
-        <f>SUM(N17:N18)</f>
+      <c r="N30" s="16">
+        <f>SUM(N28:N29)</f>
         <v>0</v>
       </c>
-      <c r="O19" s="16">
-        <f>SUM(O17:O18)</f>
+      <c r="O30" s="16">
+        <f>SUM(O28:O29)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:15">
-      <c r="B20" s="4" t="s">
+    <row r="31" spans="2:15">
+      <c r="B31" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C31" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D31" s="5">
         <v>430000</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E31" s="5">
         <v>1200</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F31" s="6">
         <f t="shared" si="2"/>
         <v>2.7906976744186047E-3</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G31" s="5">
         <f t="shared" si="3"/>
         <v>300</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H31" s="5">
         <v>360000</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I31" s="5">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J31" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K31" s="5">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L20" s="5">
+      <c r="L31" s="5">
         <v>0</v>
       </c>
-      <c r="M20" s="7">
+      <c r="M31" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N20" s="5">
+      <c r="N31" s="5">
         <v>0</v>
       </c>
-      <c r="O20" s="5">
+      <c r="O31" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:15">
-      <c r="B21" s="4"/>
-      <c r="C21" s="4" t="s">
+    <row r="32" spans="2:15">
+      <c r="B32" s="4"/>
+      <c r="C32" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D32" s="5">
         <v>280000</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E32" s="5">
         <v>640</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F32" s="6">
         <f t="shared" si="2"/>
         <v>2.2857142857142859E-3</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G32" s="5">
         <f t="shared" si="3"/>
         <v>296.875</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H32" s="5">
         <v>190000</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="5">
-        <v>0</v>
-      </c>
-      <c r="M21" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="5">
-        <v>0</v>
-      </c>
-      <c r="O21" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15">
-      <c r="B22" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="16">
-        <f>SUM(D20:D21)</f>
-        <v>710000</v>
-      </c>
-      <c r="E22" s="16">
-        <f>SUM(E20:E21)</f>
-        <v>1840</v>
-      </c>
-      <c r="F22" s="17">
-        <f t="shared" si="2"/>
-        <v>2.5915492957746477E-3</v>
-      </c>
-      <c r="G22" s="16">
-        <f t="shared" si="3"/>
-        <v>298.91304347826087</v>
-      </c>
-      <c r="H22" s="16">
-        <f>SUM(H20:H21)</f>
-        <v>550000</v>
-      </c>
-      <c r="I22" s="16">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="17">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="16">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="16">
-        <f>SUM(L20:L21)</f>
-        <v>0</v>
-      </c>
-      <c r="M22" s="18">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="16">
-        <f>SUM(N20:N21)</f>
-        <v>0</v>
-      </c>
-      <c r="O22" s="16">
-        <f>SUM(O20:O21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15">
-      <c r="B23" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" s="5">
-        <v>380000</v>
-      </c>
-      <c r="E23" s="5">
-        <v>2400</v>
-      </c>
-      <c r="F23" s="6">
-        <f t="shared" si="2"/>
-        <v>6.3157894736842104E-3</v>
-      </c>
-      <c r="G23" s="5">
-        <f t="shared" si="3"/>
-        <v>200</v>
-      </c>
-      <c r="H23" s="5">
-        <v>480000</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="4"/>
-        <v>28</v>
-      </c>
-      <c r="J23" s="6">
-        <f t="shared" si="5"/>
-        <v>1.1666666666666667E-2</v>
-      </c>
-      <c r="K23" s="5">
-        <f t="shared" si="6"/>
-        <v>17142.857142857141</v>
-      </c>
-      <c r="L23" s="5">
-        <v>560000</v>
-      </c>
-      <c r="M23" s="7">
-        <f t="shared" si="7"/>
-        <v>1.1666666666666667</v>
-      </c>
-      <c r="N23" s="5">
-        <v>18</v>
-      </c>
-      <c r="O23" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15">
-      <c r="B24" s="4"/>
-      <c r="C24" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" s="5">
-        <v>210000</v>
-      </c>
-      <c r="E24" s="5">
-        <v>1300</v>
-      </c>
-      <c r="F24" s="6">
-        <f t="shared" si="2"/>
-        <v>6.1904761904761907E-3</v>
-      </c>
-      <c r="G24" s="5">
-        <f t="shared" si="3"/>
-        <v>200</v>
-      </c>
-      <c r="H24" s="5">
-        <v>260000</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="J24" s="6">
-        <f t="shared" si="5"/>
-        <v>1.1538461538461539E-2</v>
-      </c>
-      <c r="K24" s="5">
-        <f t="shared" si="6"/>
-        <v>17333.333333333332</v>
-      </c>
-      <c r="L24" s="5">
-        <v>300000</v>
-      </c>
-      <c r="M24" s="7">
-        <f t="shared" si="7"/>
-        <v>1.1538461538461537</v>
-      </c>
-      <c r="N24" s="5">
-        <v>10</v>
-      </c>
-      <c r="O24" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15">
-      <c r="B25" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="16">
-        <f>SUM(D23:D24)</f>
-        <v>590000</v>
-      </c>
-      <c r="E25" s="16">
-        <f>SUM(E23:E24)</f>
-        <v>3700</v>
-      </c>
-      <c r="F25" s="17">
-        <f t="shared" si="2"/>
-        <v>6.2711864406779661E-3</v>
-      </c>
-      <c r="G25" s="16">
-        <f t="shared" si="3"/>
-        <v>200</v>
-      </c>
-      <c r="H25" s="16">
-        <f>SUM(H23:H24)</f>
-        <v>740000</v>
-      </c>
-      <c r="I25" s="16">
-        <f t="shared" si="4"/>
-        <v>43</v>
-      </c>
-      <c r="J25" s="17">
-        <f t="shared" si="5"/>
-        <v>1.1621621621621621E-2</v>
-      </c>
-      <c r="K25" s="16">
-        <f t="shared" si="6"/>
-        <v>17209.302325581397</v>
-      </c>
-      <c r="L25" s="16">
-        <f>SUM(L23:L24)</f>
-        <v>860000</v>
-      </c>
-      <c r="M25" s="18">
-        <f t="shared" si="7"/>
-        <v>1.1621621621621621</v>
-      </c>
-      <c r="N25" s="16">
-        <f>SUM(N23:N24)</f>
-        <v>28</v>
-      </c>
-      <c r="O25" s="16">
-        <f>SUM(O23:O24)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15">
-      <c r="B26" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D26" s="5">
-        <v>290000</v>
-      </c>
-      <c r="E26" s="5">
-        <v>1850</v>
-      </c>
-      <c r="F26" s="6">
-        <f t="shared" si="2"/>
-        <v>6.3793103448275866E-3</v>
-      </c>
-      <c r="G26" s="5">
-        <f t="shared" si="3"/>
-        <v>250.27027027027026</v>
-      </c>
-      <c r="H26" s="5">
-        <v>463000</v>
-      </c>
-      <c r="I26" s="5">
-        <f t="shared" si="4"/>
-        <v>49</v>
-      </c>
-      <c r="J26" s="6">
-        <f t="shared" si="5"/>
-        <v>2.6486486486486487E-2</v>
-      </c>
-      <c r="K26" s="5">
-        <f t="shared" si="6"/>
-        <v>9448.9795918367345</v>
-      </c>
-      <c r="L26" s="5">
-        <v>1442000</v>
-      </c>
-      <c r="M26" s="7">
-        <f t="shared" si="7"/>
-        <v>3.1144708423326133</v>
-      </c>
-      <c r="N26" s="5">
-        <v>31</v>
-      </c>
-      <c r="O26" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15">
-      <c r="B27" s="4"/>
-      <c r="C27" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D27" s="5">
-        <v>180000</v>
-      </c>
-      <c r="E27" s="5">
-        <v>980</v>
-      </c>
-      <c r="F27" s="6">
-        <f t="shared" si="2"/>
-        <v>5.4444444444444445E-3</v>
-      </c>
-      <c r="G27" s="5">
-        <f t="shared" si="3"/>
-        <v>239.79591836734693</v>
-      </c>
-      <c r="H27" s="5">
-        <v>235000</v>
-      </c>
-      <c r="I27" s="5">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-      <c r="J27" s="6">
-        <f t="shared" si="5"/>
-        <v>3.2653061224489799E-2</v>
-      </c>
-      <c r="K27" s="5">
-        <f t="shared" si="6"/>
-        <v>7343.75</v>
-      </c>
-      <c r="L27" s="5">
-        <v>794000</v>
-      </c>
-      <c r="M27" s="7">
-        <f t="shared" si="7"/>
-        <v>3.3787234042553194</v>
-      </c>
-      <c r="N27" s="5">
-        <v>20</v>
-      </c>
-      <c r="O27" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15">
-      <c r="B28" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="16">
-        <f>SUM(D26:D27)</f>
-        <v>470000</v>
-      </c>
-      <c r="E28" s="16">
-        <f>SUM(E26:E27)</f>
-        <v>2830</v>
-      </c>
-      <c r="F28" s="17">
-        <f t="shared" si="2"/>
-        <v>6.0212765957446809E-3</v>
-      </c>
-      <c r="G28" s="16">
-        <f t="shared" si="3"/>
-        <v>246.64310954063603</v>
-      </c>
-      <c r="H28" s="16">
-        <f>SUM(H26:H27)</f>
-        <v>698000</v>
-      </c>
-      <c r="I28" s="16">
-        <f t="shared" si="4"/>
-        <v>81</v>
-      </c>
-      <c r="J28" s="17">
-        <f t="shared" si="5"/>
-        <v>2.8621908127208481E-2</v>
-      </c>
-      <c r="K28" s="16">
-        <f t="shared" si="6"/>
-        <v>8617.2839506172841</v>
-      </c>
-      <c r="L28" s="16">
-        <f>SUM(L26:L27)</f>
-        <v>2236000</v>
-      </c>
-      <c r="M28" s="18">
-        <f t="shared" si="7"/>
-        <v>3.2034383954154726</v>
-      </c>
-      <c r="N28" s="16">
-        <f>SUM(N26:N27)</f>
-        <v>51</v>
-      </c>
-      <c r="O28" s="16">
-        <f>SUM(O26:O27)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15">
-      <c r="B29" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" s="5">
-        <v>471000</v>
-      </c>
-      <c r="E29" s="5">
-        <v>504</v>
-      </c>
-      <c r="F29" s="6">
-        <f t="shared" si="2"/>
-        <v>1.0700636942675159E-3</v>
-      </c>
-      <c r="G29" s="5">
-        <f t="shared" si="3"/>
-        <v>246.03174603174602</v>
-      </c>
-      <c r="H29" s="5">
-        <v>124000</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="4"/>
-        <v>114</v>
-      </c>
-      <c r="J29" s="6">
-        <f t="shared" si="5"/>
-        <v>0.22619047619047619</v>
-      </c>
-      <c r="K29" s="5">
-        <f t="shared" si="6"/>
-        <v>1087.719298245614</v>
-      </c>
-      <c r="L29" s="5">
-        <v>2956000</v>
-      </c>
-      <c r="M29" s="7">
-        <f t="shared" si="7"/>
-        <v>23.838709677419356</v>
-      </c>
-      <c r="N29" s="5">
-        <v>74</v>
-      </c>
-      <c r="O29" s="5">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15">
-      <c r="B30" s="4"/>
-      <c r="C30" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" s="5">
-        <v>260000</v>
-      </c>
-      <c r="E30" s="5">
-        <v>290</v>
-      </c>
-      <c r="F30" s="6">
-        <f t="shared" si="2"/>
-        <v>1.1153846153846153E-3</v>
-      </c>
-      <c r="G30" s="5">
-        <f t="shared" si="3"/>
-        <v>241.37931034482759</v>
-      </c>
-      <c r="H30" s="5">
-        <v>70000</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="J30" s="6">
-        <f t="shared" si="5"/>
-        <v>0.20689655172413793</v>
-      </c>
-      <c r="K30" s="5">
-        <f t="shared" si="6"/>
-        <v>1166.6666666666667</v>
-      </c>
-      <c r="L30" s="5">
-        <v>1500000</v>
-      </c>
-      <c r="M30" s="7">
-        <f t="shared" si="7"/>
-        <v>21.428571428571427</v>
-      </c>
-      <c r="N30" s="5">
-        <v>40</v>
-      </c>
-      <c r="O30" s="5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15">
-      <c r="B31" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" s="16">
-        <f>SUM(D29:D30)</f>
-        <v>731000</v>
-      </c>
-      <c r="E31" s="16">
-        <f>SUM(E29:E30)</f>
-        <v>794</v>
-      </c>
-      <c r="F31" s="17">
-        <f t="shared" si="2"/>
-        <v>1.0861833105335157E-3</v>
-      </c>
-      <c r="G31" s="16">
-        <f t="shared" si="3"/>
-        <v>244.33249370277079</v>
-      </c>
-      <c r="H31" s="16">
-        <f>SUM(H29:H30)</f>
-        <v>194000</v>
-      </c>
-      <c r="I31" s="16">
-        <f t="shared" si="4"/>
-        <v>174</v>
-      </c>
-      <c r="J31" s="17">
-        <f t="shared" si="5"/>
-        <v>0.21914357682619648</v>
-      </c>
-      <c r="K31" s="16">
-        <f t="shared" si="6"/>
-        <v>1114.9425287356321</v>
-      </c>
-      <c r="L31" s="16">
-        <f>SUM(L29:L30)</f>
-        <v>4456000</v>
-      </c>
-      <c r="M31" s="18">
-        <f t="shared" si="7"/>
-        <v>22.969072164948454</v>
-      </c>
-      <c r="N31" s="16">
-        <f>SUM(N29:N30)</f>
-        <v>114</v>
-      </c>
-      <c r="O31" s="16">
-        <f>SUM(O29:O30)</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="2:15">
-      <c r="B32" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" s="5">
-        <v>340000</v>
-      </c>
-      <c r="E32" s="5">
-        <v>1700</v>
-      </c>
-      <c r="F32" s="6">
-        <f t="shared" si="2"/>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="G32" s="5">
-        <f t="shared" si="3"/>
-        <v>150</v>
-      </c>
-      <c r="H32" s="5">
-        <v>255000</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="4"/>
@@ -15182,168 +15334,736 @@
       </c>
     </row>
     <row r="33" spans="2:15">
-      <c r="B33" s="4"/>
-      <c r="C33" s="4" t="s">
+      <c r="B33" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="16">
+        <f>SUM(D31:D32)</f>
+        <v>710000</v>
+      </c>
+      <c r="E33" s="16">
+        <f>SUM(E31:E32)</f>
+        <v>1840</v>
+      </c>
+      <c r="F33" s="17">
+        <f t="shared" si="2"/>
+        <v>2.5915492957746477E-3</v>
+      </c>
+      <c r="G33" s="16">
+        <f t="shared" si="3"/>
+        <v>298.91304347826087</v>
+      </c>
+      <c r="H33" s="16">
+        <f>SUM(H31:H32)</f>
+        <v>550000</v>
+      </c>
+      <c r="I33" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="16">
+        <f>SUM(L31:L32)</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N33" s="16">
+        <f>SUM(N31:N32)</f>
+        <v>0</v>
+      </c>
+      <c r="O33" s="16">
+        <f>SUM(O31:O32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15">
+      <c r="B34" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34" s="5">
+        <v>380000</v>
+      </c>
+      <c r="E34" s="5">
+        <v>2400</v>
+      </c>
+      <c r="F34" s="6">
+        <f t="shared" si="2"/>
+        <v>6.3157894736842104E-3</v>
+      </c>
+      <c r="G34" s="5">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="H34" s="5">
+        <v>480000</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="4"/>
+        <v>28</v>
+      </c>
+      <c r="J34" s="6">
+        <f t="shared" si="5"/>
+        <v>1.1666666666666667E-2</v>
+      </c>
+      <c r="K34" s="5">
+        <f t="shared" si="6"/>
+        <v>17142.857142857141</v>
+      </c>
+      <c r="L34" s="5">
+        <v>560000</v>
+      </c>
+      <c r="M34" s="7">
+        <f t="shared" si="7"/>
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="N34" s="5">
+        <v>18</v>
+      </c>
+      <c r="O34" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15">
+      <c r="B35" s="4"/>
+      <c r="C35" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" s="5">
+        <v>210000</v>
+      </c>
+      <c r="E35" s="5">
+        <v>1300</v>
+      </c>
+      <c r="F35" s="6">
+        <f t="shared" si="2"/>
+        <v>6.1904761904761907E-3</v>
+      </c>
+      <c r="G35" s="5">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="H35" s="5">
+        <v>260000</v>
+      </c>
+      <c r="I35" s="5">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="J35" s="6">
+        <f t="shared" si="5"/>
+        <v>1.1538461538461539E-2</v>
+      </c>
+      <c r="K35" s="5">
+        <f t="shared" si="6"/>
+        <v>17333.333333333332</v>
+      </c>
+      <c r="L35" s="5">
+        <v>300000</v>
+      </c>
+      <c r="M35" s="7">
+        <f t="shared" si="7"/>
+        <v>1.1538461538461537</v>
+      </c>
+      <c r="N35" s="5">
+        <v>10</v>
+      </c>
+      <c r="O35" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15">
+      <c r="B36" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" s="16">
+        <f>SUM(D34:D35)</f>
+        <v>590000</v>
+      </c>
+      <c r="E36" s="16">
+        <f>SUM(E34:E35)</f>
+        <v>3700</v>
+      </c>
+      <c r="F36" s="17">
+        <f t="shared" si="2"/>
+        <v>6.2711864406779661E-3</v>
+      </c>
+      <c r="G36" s="16">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="H36" s="16">
+        <f>SUM(H34:H35)</f>
+        <v>740000</v>
+      </c>
+      <c r="I36" s="16">
+        <f t="shared" si="4"/>
+        <v>43</v>
+      </c>
+      <c r="J36" s="17">
+        <f t="shared" si="5"/>
+        <v>1.1621621621621621E-2</v>
+      </c>
+      <c r="K36" s="16">
+        <f t="shared" si="6"/>
+        <v>17209.302325581397</v>
+      </c>
+      <c r="L36" s="16">
+        <f>SUM(L34:L35)</f>
+        <v>860000</v>
+      </c>
+      <c r="M36" s="18">
+        <f t="shared" si="7"/>
+        <v>1.1621621621621621</v>
+      </c>
+      <c r="N36" s="16">
+        <f>SUM(N34:N35)</f>
+        <v>28</v>
+      </c>
+      <c r="O36" s="16">
+        <f>SUM(O34:O35)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15">
+      <c r="B37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" s="5">
+        <v>290000</v>
+      </c>
+      <c r="E37" s="5">
+        <v>1850</v>
+      </c>
+      <c r="F37" s="6">
+        <f t="shared" si="2"/>
+        <v>6.3793103448275866E-3</v>
+      </c>
+      <c r="G37" s="5">
+        <f t="shared" si="3"/>
+        <v>250.27027027027026</v>
+      </c>
+      <c r="H37" s="5">
+        <v>463000</v>
+      </c>
+      <c r="I37" s="5">
+        <f t="shared" si="4"/>
+        <v>49</v>
+      </c>
+      <c r="J37" s="6">
+        <f t="shared" si="5"/>
+        <v>2.6486486486486487E-2</v>
+      </c>
+      <c r="K37" s="5">
+        <f t="shared" si="6"/>
+        <v>9448.9795918367345</v>
+      </c>
+      <c r="L37" s="5">
+        <v>1442000</v>
+      </c>
+      <c r="M37" s="7">
+        <f t="shared" si="7"/>
+        <v>3.1144708423326133</v>
+      </c>
+      <c r="N37" s="5">
+        <v>31</v>
+      </c>
+      <c r="O37" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15">
+      <c r="B38" s="4"/>
+      <c r="C38" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" s="5">
+        <v>180000</v>
+      </c>
+      <c r="E38" s="5">
+        <v>980</v>
+      </c>
+      <c r="F38" s="6">
+        <f t="shared" si="2"/>
+        <v>5.4444444444444445E-3</v>
+      </c>
+      <c r="G38" s="5">
+        <f t="shared" si="3"/>
+        <v>239.79591836734693</v>
+      </c>
+      <c r="H38" s="5">
+        <v>235000</v>
+      </c>
+      <c r="I38" s="5">
+        <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+      <c r="J38" s="6">
+        <f t="shared" si="5"/>
+        <v>3.2653061224489799E-2</v>
+      </c>
+      <c r="K38" s="5">
+        <f t="shared" si="6"/>
+        <v>7343.75</v>
+      </c>
+      <c r="L38" s="5">
+        <v>794000</v>
+      </c>
+      <c r="M38" s="7">
+        <f t="shared" si="7"/>
+        <v>3.3787234042553194</v>
+      </c>
+      <c r="N38" s="5">
+        <v>20</v>
+      </c>
+      <c r="O38" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15">
+      <c r="B39" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="16">
+        <f>SUM(D37:D38)</f>
+        <v>470000</v>
+      </c>
+      <c r="E39" s="16">
+        <f>SUM(E37:E38)</f>
+        <v>2830</v>
+      </c>
+      <c r="F39" s="17">
+        <f t="shared" si="2"/>
+        <v>6.0212765957446809E-3</v>
+      </c>
+      <c r="G39" s="16">
+        <f t="shared" si="3"/>
+        <v>246.64310954063603</v>
+      </c>
+      <c r="H39" s="16">
+        <f>SUM(H37:H38)</f>
+        <v>698000</v>
+      </c>
+      <c r="I39" s="16">
+        <f t="shared" si="4"/>
+        <v>81</v>
+      </c>
+      <c r="J39" s="17">
+        <f t="shared" si="5"/>
+        <v>2.8621908127208481E-2</v>
+      </c>
+      <c r="K39" s="16">
+        <f t="shared" si="6"/>
+        <v>8617.2839506172841</v>
+      </c>
+      <c r="L39" s="16">
+        <f>SUM(L37:L38)</f>
+        <v>2236000</v>
+      </c>
+      <c r="M39" s="18">
+        <f t="shared" si="7"/>
+        <v>3.2034383954154726</v>
+      </c>
+      <c r="N39" s="16">
+        <f>SUM(N37:N38)</f>
+        <v>51</v>
+      </c>
+      <c r="O39" s="16">
+        <f>SUM(O37:O38)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15">
+      <c r="B40" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D40" s="5">
+        <v>471000</v>
+      </c>
+      <c r="E40" s="5">
+        <v>504</v>
+      </c>
+      <c r="F40" s="6">
+        <f t="shared" si="2"/>
+        <v>1.0700636942675159E-3</v>
+      </c>
+      <c r="G40" s="5">
+        <f t="shared" si="3"/>
+        <v>246.03174603174602</v>
+      </c>
+      <c r="H40" s="5">
+        <v>124000</v>
+      </c>
+      <c r="I40" s="5">
+        <f t="shared" si="4"/>
+        <v>114</v>
+      </c>
+      <c r="J40" s="6">
+        <f t="shared" si="5"/>
+        <v>0.22619047619047619</v>
+      </c>
+      <c r="K40" s="5">
+        <f t="shared" si="6"/>
+        <v>1087.719298245614</v>
+      </c>
+      <c r="L40" s="5">
+        <v>2956000</v>
+      </c>
+      <c r="M40" s="7">
+        <f t="shared" si="7"/>
+        <v>23.838709677419356</v>
+      </c>
+      <c r="N40" s="5">
+        <v>74</v>
+      </c>
+      <c r="O40" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15">
+      <c r="B41" s="4"/>
+      <c r="C41" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D41" s="5">
+        <v>260000</v>
+      </c>
+      <c r="E41" s="5">
+        <v>290</v>
+      </c>
+      <c r="F41" s="6">
+        <f t="shared" si="2"/>
+        <v>1.1153846153846153E-3</v>
+      </c>
+      <c r="G41" s="5">
+        <f t="shared" si="3"/>
+        <v>241.37931034482759</v>
+      </c>
+      <c r="H41" s="5">
+        <v>70000</v>
+      </c>
+      <c r="I41" s="5">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="J41" s="6">
+        <f t="shared" si="5"/>
+        <v>0.20689655172413793</v>
+      </c>
+      <c r="K41" s="5">
+        <f t="shared" si="6"/>
+        <v>1166.6666666666667</v>
+      </c>
+      <c r="L41" s="5">
+        <v>1500000</v>
+      </c>
+      <c r="M41" s="7">
+        <f t="shared" si="7"/>
+        <v>21.428571428571427</v>
+      </c>
+      <c r="N41" s="5">
+        <v>40</v>
+      </c>
+      <c r="O41" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15">
+      <c r="B42" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" s="16">
+        <f>SUM(D40:D41)</f>
+        <v>731000</v>
+      </c>
+      <c r="E42" s="16">
+        <f>SUM(E40:E41)</f>
+        <v>794</v>
+      </c>
+      <c r="F42" s="17">
+        <f t="shared" si="2"/>
+        <v>1.0861833105335157E-3</v>
+      </c>
+      <c r="G42" s="16">
+        <f t="shared" si="3"/>
+        <v>244.33249370277079</v>
+      </c>
+      <c r="H42" s="16">
+        <f>SUM(H40:H41)</f>
+        <v>194000</v>
+      </c>
+      <c r="I42" s="16">
+        <f t="shared" si="4"/>
+        <v>174</v>
+      </c>
+      <c r="J42" s="17">
+        <f t="shared" si="5"/>
+        <v>0.21914357682619648</v>
+      </c>
+      <c r="K42" s="16">
+        <f t="shared" si="6"/>
+        <v>1114.9425287356321</v>
+      </c>
+      <c r="L42" s="16">
+        <f>SUM(L40:L41)</f>
+        <v>4456000</v>
+      </c>
+      <c r="M42" s="18">
+        <f t="shared" si="7"/>
+        <v>22.969072164948454</v>
+      </c>
+      <c r="N42" s="16">
+        <f>SUM(N40:N41)</f>
+        <v>114</v>
+      </c>
+      <c r="O42" s="16">
+        <f>SUM(O40:O41)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15">
+      <c r="B43" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D43" s="5">
+        <v>340000</v>
+      </c>
+      <c r="E43" s="5">
+        <v>1700</v>
+      </c>
+      <c r="F43" s="6">
+        <f t="shared" si="2"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G43" s="5">
+        <f t="shared" si="3"/>
+        <v>150</v>
+      </c>
+      <c r="H43" s="5">
+        <v>255000</v>
+      </c>
+      <c r="I43" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L43" s="5">
+        <v>0</v>
+      </c>
+      <c r="M43" s="7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N43" s="5">
+        <v>0</v>
+      </c>
+      <c r="O43" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15">
+      <c r="B44" s="4"/>
+      <c r="C44" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D44" s="5">
         <v>210000</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E44" s="5">
         <v>980</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F44" s="6">
         <f t="shared" si="2"/>
         <v>4.6666666666666671E-3</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G44" s="5">
         <f t="shared" si="3"/>
         <v>153.0612244897959</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H44" s="5">
         <v>150000</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I44" s="5">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J33" s="6">
+      <c r="J44" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K33" s="5">
+      <c r="K44" s="5">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L33" s="5">
+      <c r="L44" s="5">
         <v>0</v>
       </c>
-      <c r="M33" s="7">
+      <c r="M44" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N33" s="5">
+      <c r="N44" s="5">
         <v>0</v>
       </c>
-      <c r="O33" s="5">
+      <c r="O44" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:15">
-      <c r="B34" s="15" t="s">
+    <row r="45" spans="2:15">
+      <c r="B45" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C45" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D34" s="16">
-        <f>SUM(D32:D33)</f>
+      <c r="D45" s="16">
+        <f>SUM(D43:D44)</f>
         <v>550000</v>
       </c>
-      <c r="E34" s="16">
-        <f>SUM(E32:E33)</f>
+      <c r="E45" s="16">
+        <f>SUM(E43:E44)</f>
         <v>2680</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F45" s="17">
         <f t="shared" si="2"/>
         <v>4.8727272727272725E-3</v>
       </c>
-      <c r="G34" s="16">
+      <c r="G45" s="16">
         <f t="shared" si="3"/>
         <v>151.11940298507463</v>
       </c>
-      <c r="H34" s="16">
-        <f>SUM(H32:H33)</f>
+      <c r="H45" s="16">
+        <f>SUM(H43:H44)</f>
         <v>405000</v>
       </c>
-      <c r="I34" s="16">
+      <c r="I45" s="16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J34" s="17">
+      <c r="J45" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K34" s="16">
+      <c r="K45" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L34" s="16">
-        <f>SUM(L32:L33)</f>
+      <c r="L45" s="16">
+        <f>SUM(L43:L44)</f>
         <v>0</v>
       </c>
-      <c r="M34" s="18">
+      <c r="M45" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N34" s="16">
-        <f>SUM(N32:N33)</f>
+      <c r="N45" s="16">
+        <f>SUM(N43:N44)</f>
         <v>0</v>
       </c>
-      <c r="O34" s="16">
-        <f>SUM(O32:O33)</f>
+      <c r="O45" s="16">
+        <f>SUM(O43:O44)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:15">
-      <c r="B35" s="30" t="s">
+    <row r="46" spans="2:15">
+      <c r="B46" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="12">
-        <f>D13+D16+D19+D22+D25+D28+D31+D34</f>
+      <c r="C46" s="30"/>
+      <c r="D46" s="12">
+        <f>D24+D27+D30+D33+D36+D39+D42+D45</f>
         <v>7051000</v>
       </c>
-      <c r="E35" s="12">
-        <f>E13+E16+E19+E22+E25+E28+E31+E34</f>
+      <c r="E46" s="12">
+        <f>E24+E27+E30+E33+E36+E39+E42+E45</f>
         <v>35884</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F46" s="13">
         <f t="shared" si="2"/>
         <v>5.0892072046518225E-3</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G46" s="12">
         <f t="shared" si="3"/>
         <v>219.84728569836139</v>
       </c>
-      <c r="H35" s="12">
-        <f>H13+H16+H19+H22+H25+H28+H31+H34</f>
+      <c r="H46" s="12">
+        <f>H24+H27+H30+H33+H36+H39+H42+H45</f>
         <v>7889000</v>
       </c>
-      <c r="I35" s="12">
+      <c r="I46" s="12">
         <f t="shared" si="4"/>
         <v>910</v>
       </c>
-      <c r="J35" s="13">
+      <c r="J46" s="13">
         <f t="shared" si="5"/>
         <v>2.5359491695463161E-2</v>
       </c>
-      <c r="K35" s="12">
+      <c r="K46" s="12">
         <f t="shared" si="6"/>
         <v>8669.2307692307695</v>
       </c>
-      <c r="L35" s="12">
-        <f>L13+L16+L19+L22+L25+L28+L31+L34</f>
+      <c r="L46" s="12">
+        <f>L24+L27+L30+L33+L36+L39+L42+L45</f>
         <v>11478000</v>
       </c>
-      <c r="M35" s="14">
+      <c r="M46" s="14">
         <f t="shared" si="7"/>
         <v>1.4549372544048675</v>
       </c>
-      <c r="N35" s="12">
-        <f>N13+N16+N19+N22+N25+N28+N31+N34</f>
+      <c r="N46" s="12">
+        <f>N24+N27+N30+N33+N36+N39+N42+N45</f>
         <v>573</v>
       </c>
-      <c r="O35" s="12">
-        <f>O13+O16+O19+O22+O25+O28+O31+O34</f>
+      <c r="O46" s="12">
+        <f>O24+O27+O30+O33+O36+O39+O42+O45</f>
         <v>337</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B9:O9"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B20:O20"/>
+    <mergeCell ref="B46:C46"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="C6:N7">
@@ -15356,6 +16076,7 @@
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -17080,4 +17801,522 @@
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr>
+    <tabColor theme="8" tint="0.79998168889431442"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:P11"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="2.42578125" customWidth="1"/>
+    <col min="2" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="30.7109375" customWidth="1"/>
+    <col min="5" max="12" width="11.140625" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="16" width="11.140625" customWidth="1"/>
+    <col min="17" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="16384" width="8.7109375" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:16" ht="24" customHeight="1">
+      <c r="B2" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+    </row>
+    <row r="3" spans="2:16" ht="30" customHeight="1">
+      <c r="B3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16">
+      <c r="B4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="5">
+        <v>18000</v>
+      </c>
+      <c r="F4" s="5">
+        <v>420</v>
+      </c>
+      <c r="G4" s="6">
+        <f t="shared" ref="G4:G11" si="0">IFERROR(F4/E4,0)</f>
+        <v>2.3333333333333334E-2</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" ref="H4:H11" si="1">IFERROR(I4/F4,0)</f>
+        <v>1523.8095238095239</v>
+      </c>
+      <c r="I4" s="5">
+        <v>640000</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" ref="J4:J11" si="2">O4+P4</f>
+        <v>80</v>
+      </c>
+      <c r="K4" s="6">
+        <f t="shared" ref="K4:K11" si="3">IFERROR(J4/F4,0)</f>
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="L4" s="5">
+        <f t="shared" ref="L4:L11" si="4">IFERROR(I4/J4,0)</f>
+        <v>8000</v>
+      </c>
+      <c r="M4" s="5">
+        <v>2200000</v>
+      </c>
+      <c r="N4" s="7">
+        <f t="shared" ref="N4:N11" si="5">IFERROR(M4/I4,0)</f>
+        <v>3.4375</v>
+      </c>
+      <c r="O4" s="23">
+        <v>55</v>
+      </c>
+      <c r="P4" s="23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="5">
+        <v>12000</v>
+      </c>
+      <c r="F5" s="5">
+        <v>300</v>
+      </c>
+      <c r="G5" s="6">
+        <f t="shared" si="0"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="H5" s="5">
+        <f t="shared" si="1"/>
+        <v>1533.3333333333333</v>
+      </c>
+      <c r="I5" s="5">
+        <v>460000</v>
+      </c>
+      <c r="J5" s="5">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="K5" s="6">
+        <f t="shared" si="3"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="L5" s="5">
+        <f t="shared" si="4"/>
+        <v>11500</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1100000</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="5"/>
+        <v>2.3913043478260869</v>
+      </c>
+      <c r="O5" s="23">
+        <v>28</v>
+      </c>
+      <c r="P5" s="23">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="5">
+        <v>9000</v>
+      </c>
+      <c r="F6" s="5">
+        <v>180</v>
+      </c>
+      <c r="G6" s="6">
+        <f t="shared" si="0"/>
+        <v>0.02</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" si="1"/>
+        <v>1444.4444444444443</v>
+      </c>
+      <c r="I6" s="5">
+        <v>260000</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="K6" s="6">
+        <f t="shared" si="3"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="L6" s="5">
+        <f t="shared" si="4"/>
+        <v>21666.666666666668</v>
+      </c>
+      <c r="M6" s="5">
+        <v>300000</v>
+      </c>
+      <c r="N6" s="7">
+        <f t="shared" si="5"/>
+        <v>1.1538461538461537</v>
+      </c>
+      <c r="O6" s="23">
+        <v>8</v>
+      </c>
+      <c r="P6" s="23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="16">
+        <f>SUM(E4:E6)</f>
+        <v>39000</v>
+      </c>
+      <c r="F7" s="16">
+        <f>SUM(F4:F6)</f>
+        <v>900</v>
+      </c>
+      <c r="G7" s="17">
+        <f t="shared" si="0"/>
+        <v>2.3076923076923078E-2</v>
+      </c>
+      <c r="H7" s="16">
+        <f t="shared" si="1"/>
+        <v>1511.1111111111111</v>
+      </c>
+      <c r="I7" s="16">
+        <f>SUM(I4:I6)</f>
+        <v>1360000</v>
+      </c>
+      <c r="J7" s="16">
+        <f t="shared" si="2"/>
+        <v>132</v>
+      </c>
+      <c r="K7" s="17">
+        <f t="shared" si="3"/>
+        <v>0.14666666666666667</v>
+      </c>
+      <c r="L7" s="16">
+        <f t="shared" si="4"/>
+        <v>10303.030303030304</v>
+      </c>
+      <c r="M7" s="16">
+        <f>SUM(M4:M6)</f>
+        <v>3600000</v>
+      </c>
+      <c r="N7" s="18">
+        <f t="shared" si="5"/>
+        <v>2.6470588235294117</v>
+      </c>
+      <c r="O7" s="24">
+        <f>SUM(O4:O6)</f>
+        <v>91</v>
+      </c>
+      <c r="P7" s="24">
+        <f>SUM(P4:P6)</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16">
+      <c r="B8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="5">
+        <v>10000</v>
+      </c>
+      <c r="F8" s="5">
+        <v>220</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" si="0"/>
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="H8" s="5">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="I8" s="5">
+        <v>330000</v>
+      </c>
+      <c r="J8" s="5">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="K8" s="6">
+        <f t="shared" si="3"/>
+        <v>8.1818181818181818E-2</v>
+      </c>
+      <c r="L8" s="5">
+        <f t="shared" si="4"/>
+        <v>18333.333333333332</v>
+      </c>
+      <c r="M8" s="5">
+        <v>720000</v>
+      </c>
+      <c r="N8" s="7">
+        <f t="shared" si="5"/>
+        <v>2.1818181818181817</v>
+      </c>
+      <c r="O8" s="23">
+        <v>12</v>
+      </c>
+      <c r="P8" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="5">
+        <v>8000</v>
+      </c>
+      <c r="F9" s="5">
+        <v>100</v>
+      </c>
+      <c r="G9" s="6">
+        <f t="shared" si="0"/>
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="H9" s="5">
+        <f t="shared" si="1"/>
+        <v>1600</v>
+      </c>
+      <c r="I9" s="5">
+        <v>160000</v>
+      </c>
+      <c r="J9" s="5">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="K9" s="6">
+        <f t="shared" si="3"/>
+        <v>0.11</v>
+      </c>
+      <c r="L9" s="5">
+        <f t="shared" si="4"/>
+        <v>14545.454545454546</v>
+      </c>
+      <c r="M9" s="5">
+        <v>440000</v>
+      </c>
+      <c r="N9" s="7">
+        <f t="shared" si="5"/>
+        <v>2.75</v>
+      </c>
+      <c r="O9" s="23">
+        <v>8</v>
+      </c>
+      <c r="P9" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16">
+      <c r="B10" s="15"/>
+      <c r="C10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="16">
+        <f>SUM(E8:E9)</f>
+        <v>18000</v>
+      </c>
+      <c r="F10" s="16">
+        <f>SUM(F8:F9)</f>
+        <v>320</v>
+      </c>
+      <c r="G10" s="17">
+        <f t="shared" si="0"/>
+        <v>1.7777777777777778E-2</v>
+      </c>
+      <c r="H10" s="16">
+        <f t="shared" si="1"/>
+        <v>1531.25</v>
+      </c>
+      <c r="I10" s="16">
+        <f>SUM(I8:I9)</f>
+        <v>490000</v>
+      </c>
+      <c r="J10" s="16">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="K10" s="17">
+        <f t="shared" si="3"/>
+        <v>9.0624999999999997E-2</v>
+      </c>
+      <c r="L10" s="16">
+        <f t="shared" si="4"/>
+        <v>16896.551724137931</v>
+      </c>
+      <c r="M10" s="16">
+        <f>SUM(M8:M9)</f>
+        <v>1160000</v>
+      </c>
+      <c r="N10" s="18">
+        <f t="shared" si="5"/>
+        <v>2.3673469387755102</v>
+      </c>
+      <c r="O10" s="24">
+        <f>SUM(O8:O9)</f>
+        <v>20</v>
+      </c>
+      <c r="P10" s="24">
+        <f>SUM(P8:P9)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16">
+      <c r="B11" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="12">
+        <f>E7+E10</f>
+        <v>57000</v>
+      </c>
+      <c r="F11" s="12">
+        <f>F7+F10</f>
+        <v>1220</v>
+      </c>
+      <c r="G11" s="13">
+        <f t="shared" si="0"/>
+        <v>2.1403508771929824E-2</v>
+      </c>
+      <c r="H11" s="12">
+        <f t="shared" si="1"/>
+        <v>1516.3934426229507</v>
+      </c>
+      <c r="I11" s="12">
+        <f>I7+I10</f>
+        <v>1850000</v>
+      </c>
+      <c r="J11" s="12">
+        <f t="shared" si="2"/>
+        <v>161</v>
+      </c>
+      <c r="K11" s="13">
+        <f t="shared" si="3"/>
+        <v>0.13196721311475409</v>
+      </c>
+      <c r="L11" s="12">
+        <f t="shared" si="4"/>
+        <v>11490.683229813665</v>
+      </c>
+      <c r="M11" s="12">
+        <f>M7+M10</f>
+        <v>4760000</v>
+      </c>
+      <c r="N11" s="14">
+        <f t="shared" si="5"/>
+        <v>2.5729729729729729</v>
+      </c>
+      <c r="O11" s="25">
+        <f>O7+O10</f>
+        <v>111</v>
+      </c>
+      <c r="P11" s="25">
+        <f>P7+P10</f>
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B11:D11"/>
+  </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
 </file>
--- a/src/assets/report-template.xlsx
+++ b/src/assets/report-template.xlsx
@@ -3299,7 +3299,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>일자별 광고비·매출</a:t>
+              <a:t>일자별 광고비&amp;매출</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3398,8 +3398,8 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:marker val="1"/>
-        <c:axId val="811110003"/>
-        <c:axId val="811110004"/>
+        <c:axId val="811110001"/>
+        <c:axId val="811110002"/>
       </c:lineChart>
       <c:catAx>
         <c:axId val="811110001"/>
@@ -3487,59 +3487,6 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
-      <c:valAx>
-        <c:axId val="811110004"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="r"/>
-        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="0">
-            <a:noFill/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ko-KR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="811110003"/>
-        <c:crosses val="max"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:catAx>
-        <c:axId val="811110003"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="811110004"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
       <c:spPr>
         <a:noFill/>
         <a:ln w="0">
@@ -3612,7 +3559,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>일자별 광고비·매출</a:t>
+              <a:t>일자별 광고비&amp;매출</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3711,8 +3658,8 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:marker val="1"/>
-        <c:axId val="811110003"/>
-        <c:axId val="811110004"/>
+        <c:axId val="811110001"/>
+        <c:axId val="811110002"/>
       </c:lineChart>
       <c:catAx>
         <c:axId val="811110001"/>
@@ -3800,59 +3747,6 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
-      <c:valAx>
-        <c:axId val="811110004"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="r"/>
-        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="0">
-            <a:noFill/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ko-KR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="811110003"/>
-        <c:crosses val="max"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:catAx>
-        <c:axId val="811110003"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="none"/>
-        <c:crossAx val="811110004"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
       <c:spPr>
         <a:noFill/>
         <a:ln w="0">
@@ -4436,7 +4330,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
@@ -4449,7 +4343,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="1" strike="noStrike" spc="-1">
+              <a:defRPr sz="1400" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -4457,13 +4351,13 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1200" b="1" strike="noStrike" spc="-1">
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1400" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>일자별 추이</a:t>
+              <a:t>일자별 광고비&amp;매출</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4479,21 +4373,52 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
+              <c:f>검색_상세!$G$14</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>검색_상세!$B$15:$B$21</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>검색_상세!$G$15:$G$21</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="60"/>
+        <c:overlap val="0"/>
+        <c:axId val="811110001"/>
+        <c:axId val="811110002"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
               <c:f>검색_상세!$K$14</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>매출액</c:v>
-                </c:pt>
-              </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -4518,264 +4443,24 @@
               </a:ln>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="ko-KR"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="1"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>검색_상세!$B$15:$B$21</c:f>
-              <c:strCache>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>06/15 (월)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>06/16 (화)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>06/17 (수)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>06/18 (목)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>06/19 (금)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>06/20 (토)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>06/21 (일)</c:v>
-                </c:pt>
-              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>검색_상세!$K$15:$K$21</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>2500000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2300000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2400000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2150000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2250000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2600000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2400000</c:v>
-                </c:pt>
-              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A33A-4F32-95A2-48A9CD9093D3}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>검색_상세!$G$14</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>총비용</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="21960">
-              <a:solidFill>
-                <a:srgbClr val="0070C0"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="0070C0"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:schemeClr val="bg1"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="ko-KR"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="1"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>검색_상세!$B$15:$B$21</c:f>
-              <c:strCache>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>06/15 (월)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>06/16 (화)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>06/17 (수)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>06/18 (목)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>06/19 (금)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>06/20 (토)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>06/21 (일)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>검색_상세!$G$15:$G$21</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>920000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>880000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>900000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>850000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>870000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>940000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>840000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A33A-4F32-95A2-48A9CD9093D3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:hiLowLines>
-          <c:spPr>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:hiLowLines>
         <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="78718358"/>
-        <c:axId val="75035427"/>
+        <c:axId val="811110001"/>
+        <c:axId val="811110002"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="78718358"/>
+        <c:axId val="811110001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4808,7 +4493,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75035427"/>
+        <c:crossAx val="811110002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4816,22 +4501,29 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="75035427"/>
+        <c:axId val="811110002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
+          <a:ln w="0">
+            <a:noFill/>
           </a:ln>
         </c:spPr>
         <c:txPr>
@@ -4849,7 +4541,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78718358"/>
+        <c:crossAx val="811110001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4887,24 +4579,13 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:round/>
+    <a:noFill/>
+    <a:ln w="0">
+      <a:noFill/>
     </a:ln>
   </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
@@ -5893,7 +5574,7 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
@@ -5906,7 +5587,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr altLang="en-US" sz="1400" b="1" strike="noStrike" spc="-1">
+              <a:defRPr sz="1400" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -5914,8 +5595,13 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ko-KR" sz="1400"/>
-              <a:t>일자별 추이</a:t>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1400" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>일자별 광고비&amp;매출</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -5931,154 +5617,52 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>디스플레이_상세!$K$14</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>매출액</c:v>
-                </c:pt>
-              </c:strCache>
+              <c:f>디스플레이_상세!$G$14</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="21960">
-              <a:solidFill>
-                <a:srgbClr val="0070C0"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:ln>
-                <a:solidFill>
-                  <a:schemeClr val="bg1"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="ko-KR"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="1"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>디스플레이_상세!$B$15:$B$21</c:f>
-              <c:strCache>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>06/15 (월)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>06/16 (화)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>06/17 (수)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>06/18 (목)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>06/19 (금)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>06/20 (토)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>06/21 (일)</c:v>
-                </c:pt>
-              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>디스플레이_상세!$K$15:$K$21</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>1250000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1150000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1300000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1100000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1200000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1400000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1300000</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:f>디스플레이_상세!$G$15:$G$21</c:f>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EE25-42EE-BBF4-124C3BA08252}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
+        <c:gapWidth val="60"/>
+        <c:overlap val="0"/>
+        <c:axId val="811110001"/>
+        <c:axId val="811110002"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>디스플레이_상세!$G$14</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>총비용</c:v>
-                </c:pt>
-              </c:strCache>
+              <c:f>디스플레이_상세!$K$14</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -6103,128 +5687,24 @@
               </a:ln>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="ko-KR"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="1"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>디스플레이_상세!$B$15:$B$21</c:f>
-              <c:strCache>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>06/15 (월)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>06/16 (화)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>06/17 (수)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>06/18 (목)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>06/19 (금)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>06/20 (토)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>06/21 (일)</c:v>
-                </c:pt>
-              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>디스플레이_상세!$G$15:$G$21</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>760000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>730000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>770000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>720000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>740000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>800000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>760000</c:v>
-                </c:pt>
-              </c:numCache>
+              <c:f>디스플레이_상세!$K$15:$K$21</c:f>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EE25-42EE-BBF4-124C3BA08252}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:hiLowLines>
-          <c:spPr>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:hiLowLines>
         <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="17044211"/>
-        <c:axId val="16225181"/>
+        <c:axId val="811110001"/>
+        <c:axId val="811110002"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="17044211"/>
+        <c:axId val="811110001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6257,7 +5737,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16225181"/>
+        <c:crossAx val="811110002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6265,22 +5745,29 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16225181"/>
+        <c:axId val="811110002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
+          <a:ln w="0">
+            <a:noFill/>
           </a:ln>
         </c:spPr>
         <c:txPr>
@@ -6298,7 +5785,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17044211"/>
+        <c:crossAx val="811110001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6323,7 +5810,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1200" b="0" strike="noStrike" spc="-1">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -6336,24 +5823,13 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:round/>
+    <a:noFill/>
+    <a:ln w="0">
+      <a:noFill/>
     </a:ln>
   </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
@@ -8366,13 +7842,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>59070</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>714374</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>247650</xdr:rowOff>
     </xdr:to>
@@ -8401,13 +7877,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>59070</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>714374</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>247650</xdr:rowOff>
     </xdr:to>
@@ -11443,7 +10919,7 @@
     <mergeCell ref="B38:C38"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="C6:N7">
+  <conditionalFormatting sqref="C17:N18">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -16066,7 +15542,7 @@
     <mergeCell ref="B46:C46"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="C6:N7">
+  <conditionalFormatting sqref="C17:N18">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
